--- a/data/Guia/Identity_Empresa_v2.xlsx
+++ b/data/Guia/Identity_Empresa_v2.xlsx
@@ -1,32 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IvanEstebanMateusSoc\Documents\Ivan\Claude\BOT MAESTRO MARKETING\timekeepers-workspace\data\Guia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ivanmateus1015/Documents/Ivan/Claude/Bot maestro/Marketing_Bot/data/Guia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B49EA1-93EA-4EFB-A06D-BE1CF3613E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CBDBEE6-5DFC-E846-9377-6F47672CBCC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="48096" yWindow="20628" windowWidth="17280" windowHeight="9960" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71940" yWindow="4180" windowWidth="29920" windowHeight="17220" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📘 INSTRUCCIONES" sheetId="1" r:id="rId1"/>
     <sheet name="DRAKEN" sheetId="2" r:id="rId2"/>
     <sheet name="URBEX" sheetId="3" r:id="rId3"/>
     <sheet name="MARIA_FERNANDA" sheetId="4" r:id="rId4"/>
-    <sheet name="PLANTILLA_VACIA" sheetId="5" r:id="rId5"/>
-    <sheet name="📚 DICCIONARIO_CAMPOS" sheetId="6" r:id="rId6"/>
-    <sheet name="🆕 CAMBIOS_V2" sheetId="7" r:id="rId7"/>
+    <sheet name="LUNAMARTE" sheetId="8" r:id="rId5"/>
+    <sheet name="PLANTILLA_VACIA" sheetId="5" r:id="rId6"/>
+    <sheet name="📚 DICCIONARIO_CAMPOS" sheetId="6" r:id="rId7"/>
+    <sheet name="🆕 CAMBIOS_V2" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1503" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1807" uniqueCount="417">
   <si>
     <t>TIMEKEEPERS AI — IDENTITY EMPRESA v2.0</t>
   </si>
@@ -1151,6 +1152,167 @@
   </si>
   <si>
     <t>Ticket medio-alto / Alto (Proyectos integrales).</t>
+  </si>
+  <si>
+    <t>Lunamarte Studio LLC (nombre comercial: Lunamarte Studio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunamarte Studio es un estudio de estética facial personalizada ubicado en Naples, FL, dentro de Cloud 9 Med Spa. Trabaja con mujeres que deciden envejecer de forma consciente, cuidando su piel con intención, estrategia y sostenibilidad. Cada tratamiento parte de un diagnóstico real y personalizado — no de tendencias. La misión es elevar los estándares de bienestar de cada mujer que entra al estudio: no solo su piel, sino su relación con ella misma.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cálido · Empático · Consciente/Intencional · Cercano (nunca clínico) · Seguro. Inferido de: (1) el lenguaje de la propia marca — "envejecer de forma consciente", "con intención"; (2) el perfil de Mila, que rechaza tono frío/clínico y busca sentirse acompañada sin juicio; (3) la restricción explícita de no usar lenguaje de urgencia ni de "milagro".
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Filosofía y método — "envejecer consciente" vs. tendencias.2) Educación de piel — rutinas, mitos, diagnóstico real.3) Bienestar emocional — autocuidado como decisión, no lujo.4) Leticia como rostro humano — proceso, cuidado individual.5) Resultados reales — antes/después honestos, testimonios.6) Estilo de vida de Mila — equilibrio, gym, crecimiento personal.Inferido combinando el foco estratégico del mes (L), el perfil de Mila (F) y las restricciones de marca (I).
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No hay oferta puntual este mes. Decisión explícita del cliente: no comunicar un tratamiento específico, sino la metodología/filosofía de marca </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mujer latina de 25-45 años en EE.UU. (foco Naples, FL), NSE medio-alto (ingresos $4,000+/mes), profesional, dueña de negocio o mamá ocupada. Le interesan el gym, el bienestar y el crecimiento personal. Su frustración central es no saber qué hacer con su piel: se siente confundida, sin tiempo y se compara con otras mujeres. No busca solo vanidad — busca equilibrio, bienestar emocional y un espacio sin juicio que le devuelva confianza.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">facial en Naples FL, estética facial Naples, spa facial Naples Florida, tratamientos faciales personalizados, esthetician Naples FL, spa boutique Naples, diagnóstico de piel personalizado, envejecimiento consciente, skincare para mujeres latinas, dermaplaning Naples, deep reset facial, facial sculpt massage, back facial Naples, body relax massage Naples FL, depilación cejas Naples, Cloud 9 Med Spa facial, skin serenity ritual, cuidado de piel sostenible, rutina facial personalizada, radiance glow facial. Inferido del catálogo de servicios (P) y la ubicación (K) — validar volumen de búsqueda real antes de usar en SEO pago.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My skin is much more hydrated , the etraction of pimples was not painful and in addition to that the products and everything she does, I don't let my face get inflamed or have irritation! 
+She really cares about your skin and your well-being it was a wonderful experience. It was a momento for myself. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">No prometer resultados inmediatos ni usar lenguaje de "milagro"/"solución rápida". No hacer comparaciones directas con otros spas o estéticas. No mostrar procedimientos invasivos o médicos (Lunamarte es estética, no medicina). No usar lenguaje de tendencias ("tratamiento viral", "lo que está de moda").
+</t>
+  </si>
+  <si>
+    <t>Estética facial personalizada / bienestar y belleza — spa boutique, no medicina estética.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal: Naples, FL. 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Posicionar la nueva visión/metodología de Lunamarte. Instalar en la audiencia que los resultados reales vienen de un plan personalizado y sostenible, no de seguir tendencias. Conversación central: mujeres comprometidas con cambios visibles y duraderos vs. mujeres que persiguen soluciones rápidas.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Diagnóstico real y personalizado antes de cualquier tratamiento — no protocolo genérico.2) Filosofía de sostenibilidad: un plan que evoluciona con la clienta, no una solución puntual.3) Relación humana directa con la fundadora/esthetician (Leticia) — no técnicos rotativos.4) Enfoque en bienestar emocional integral, no solo resultado estético.Inferido de la descripción de marca (B), el diferenciador #1 (Y) y el motivo por el que cierran venta ("qué hace que un cliente diga que sí").
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tendencias de "slow beauty" / skincare consciente, envejecimiento saludable, wellness holístico, autocuidado emocional en mujeres latinas. Evitar activamente tendencias virales de "quick fix". Inferido de la filosofía de marca — validar con Leticia si hay temas puntuales de interés.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tendencias estéticas pasajeras, comparaciones de precio como argumento de venta, lenguaje de presión/urgencia artificial, nombres de competidores.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FACIAL TREATMENTS: Custom Facial Treatment (desde $89) · Deep Reset Facial (desde $89) · Event Facial con dermaplaning (desde $120) · Facial Sculpt Massage (desde $140) · Radiance Glow Facial (desde $160) · Skin Serenity Ritual (desde $120).BODY TREATMENTS: Back Facial (desde $120) · Body Relax Massage, en studio y a domicilio (desde $120).WAXING: Cejas &amp; Underarms (desde $30).Rango general: $89 – $260.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diagnóstico personalizado | Envejecimiento consciente | Bienestar emocional y autocuidado | Sostenibilidad de resultados | Educación de piel (rutinas y mitos) | Filosofía e historia de Leticia | Testimonios y resultados reales | Equilibrio vida-bienestar. Inferido cruzando pilares de contenido (D), diferenciador (Y) y buyer persona (F).
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slow beauty / skin longevity y wellness holístico (marcas de filosofía similar a "menos tendencia, más plan sostenible"), sin nombrar competidores directos locales. Inferido — opcional, validar con Leticia si hay referentes concretos.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Century Expanded (cuerpo principal) · Zalando Sans (textos secundarios) · Pinyon Script (acento caligráfico).
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#LunamarteStudio · #Lunamartefacialsnaples
+</t>
+  </si>
+  <si>
+    <t>#EnvejecerConsciente #SkinCareConIntencion #NaplesFL #EstheticianNaples #BienestarFemenino #PielConProposito #AutocuidadoReal #MujeresQueSeCuidan. Inferido del posicionamiento y tagline propuestos — validar con Leticia antes de usarlos como estándar fijo.</t>
+  </si>
+  <si>
+    <t>#GlowUp #SkincareHacks #ViralFacial #TrendingNow #InstantResults #MiracleSkin, y cualquier hashtag que mencione competidores locales. Inferido directamente de las restricciones ya confirmadas (I, O).</t>
+  </si>
+  <si>
+    <t>✨ 🤍 🌿 🕊️ 😌 — tono cálido y elegante, coherente con "consciente" y "sin juicio". Inferido del tono de voz (C) y el posicionamiento premium-boutique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">😂 🔥 💯 😜 🎉 💰 — demasiado casuales/virales o asociados a urgencia y "hype", lo que choca con la restricción de no lenguaje de tendencia ni presión.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Español como idioma principal. Naples, FL tiene también una base angloparlante amplia, así que contenido bilingüe (subtítulos/captions en inglés) podría ampliar alcance sin cambiar el tono. Inferido de la ubicación y el perfil de Mila (latina en EE.UU.) — confirmar con Leticia si ya maneja inglés en algún canal.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Mila" — mujer latina de 25 a 45 años, residente en EE.UU. (foco Naples, FL).
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-45 años · NSE medio-alto (ingresos $4,000+/mes) · profesional, dueña de negocio o mamá ocupada · soltera o casada, con o sin hijos.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) No sabe qué hacer con su piel — se siente confundida y sin tiempo. 2) Emocionalmente cargada, se compara con otras mujeres que "avanzan más". 3) Ha dejado de cuidarse por etapas difíciles y quiere recuperar seguridad en sí misma.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrata equilibrio y bienestar emocional: un espacio de acompañamiento sin juicio que le devuelva confianza — no solo un tratamiento estético.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) "No tengo tiempo." 2) "Esto no es para mí" (por precio o por no sentirse el "tipo" de mujer que va a un estudio así). 3) "No sé si lo puedo sostener" (tiempo, consistencia, presupuesto). 4) "¿Y si no veo resultados reales?" — desconfianza tras probar otras soluciones que no funcionaron. 5) "Puedo hacerlo yo misma en casa" — no percibe aún el valor del diagnóstico profesional. Las dos últimas son inferidas a partir del perfil de Mila (comparación con otras, frustración por soluciones fallidas) — validar con Leticia si coinciden con lo que escucha en consulta.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gimnasio y bienestar físico · crecimiento personal · invertir en sí mismas con intención; sentirse acompañadas y sin juicio.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Envejecer con intención. Un plan que evoluciona contigo." Inferido directamente del lenguaje ya usado por la propia marca en su descripción (B) y foco estratégico (L) — es casi una cita textual reformulada como tagline, no una invención.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No somos medicina estética ni procedimientos invasivos. No seguimos tendencias virales. No competimos por precio ni comparamos con otros spas o estéticas.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La relación humana genuina con Leticia: el cliente siente que hay una persona real detrás de la marca que conoce su piel y se involucra en sus resultados — eso cierra la venta, no las promociones.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$89 – $260 (rango general de servicios).
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planificación de contenido mensual. Feed: Mafe publica de forma autónoma en el mes ya aprobado. Stories: a cargo de Leticia.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fundadora y Esthetician — Leticia González (IG @leticiagonzalez___, WhatsApp 305-297-1694).
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aprobación del plan mensual completo por Leticia — no aprobación pieza por pieza.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El plan se aprueba durante la última semana del mes anterior. Una vez aprobado, no se requiere aprobación adicional por publicación individual.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No mencionar competidores por nombre; no lenguaje de urgencia/presión; no contenido de procedimientos médicos o invasivos.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slow beauty, skin longevity, envejecimiento saludable, wellness emocional femenino. Mismo criterio que N — inferido, validar con Leticia.
+</t>
+  </si>
+  <si>
+    <t>IDENTITY: LUNAMARTE</t>
   </si>
 </sst>
 </file>
@@ -1160,7 +1322,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1173,90 +1335,106 @@
       <sz val="20"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="12"/>
       <color rgb="FFB8941F"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color rgb="FF0A1F44"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF0A1F44"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF555555"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF0A1F44"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFC0392B"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FFC00000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF7F8C8D"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
@@ -1283,8 +1461,45 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0B0F19"/>
+      <name val="Inter"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1357,6 +1572,66 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0A1F44"/>
+        <bgColor rgb="FF0A1F44"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8941F"/>
+        <bgColor rgb="FFB8941F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E4F5"/>
+        <bgColor rgb="FFD6E4F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE5B4"/>
+        <bgColor rgb="FFFFE5B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8DFF5"/>
+        <bgColor rgb="FFE8DFF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF4B8"/>
+        <bgColor rgb="FFFFF4B8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4F1D4"/>
+        <bgColor rgb="FFD4F1D4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD4D4"/>
+        <bgColor rgb="FFFFD4D4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD8B1"/>
+        <bgColor rgb="FFFFD8B1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4D4D4"/>
+        <bgColor rgb="FFD4D4D4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1400,7 +1675,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1478,10 +1753,26 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1524,27 +1815,109 @@
     <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1849,222 +2222,222 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
     <col min="2" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:4" ht="40" customHeight="1">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
       <c r="D1" s="28"/>
     </row>
-    <row r="2" spans="1:4" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="48" t="s">
+    <row r="2" spans="1:4" ht="25" customHeight="1">
+      <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
     </row>
-    <row r="5" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="47" t="s">
+    <row r="5" spans="1:4" ht="22" customHeight="1">
+      <c r="A5" s="30" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
       <c r="D5" s="28"/>
     </row>
-    <row r="6" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="46" t="s">
+    <row r="6" spans="1:4" ht="20" customHeight="1">
+      <c r="A6" s="29" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="28"/>
       <c r="C6" s="28"/>
       <c r="D6" s="28"/>
     </row>
-    <row r="8" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="47" t="s">
+    <row r="8" spans="1:4" ht="22" customHeight="1">
+      <c r="A8" s="30" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="28"/>
       <c r="C8" s="28"/>
       <c r="D8" s="28"/>
     </row>
-    <row r="9" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="46" t="s">
+    <row r="9" spans="1:4" ht="20" customHeight="1">
+      <c r="A9" s="29" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="28"/>
       <c r="C9" s="28"/>
       <c r="D9" s="28"/>
     </row>
-    <row r="10" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="46" t="s">
+    <row r="10" spans="1:4" ht="20" customHeight="1">
+      <c r="A10" s="29" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="28"/>
       <c r="C10" s="28"/>
       <c r="D10" s="28"/>
     </row>
-    <row r="11" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="46" t="s">
+    <row r="11" spans="1:4" ht="20" customHeight="1">
+      <c r="A11" s="29" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="28"/>
     </row>
-    <row r="12" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:4" ht="20" customHeight="1">
+      <c r="A12" s="29" t="s">
         <v>8</v>
       </c>
       <c r="B12" s="28"/>
       <c r="C12" s="28"/>
       <c r="D12" s="28"/>
     </row>
-    <row r="13" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="46" t="s">
+    <row r="13" spans="1:4" ht="20" customHeight="1">
+      <c r="A13" s="29" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="28"/>
       <c r="C13" s="28"/>
       <c r="D13" s="28"/>
     </row>
-    <row r="14" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="46" t="s">
+    <row r="14" spans="1:4" ht="20" customHeight="1">
+      <c r="A14" s="29" t="s">
         <v>10</v>
       </c>
       <c r="B14" s="28"/>
       <c r="C14" s="28"/>
       <c r="D14" s="28"/>
     </row>
-    <row r="16" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="47" t="s">
+    <row r="16" spans="1:4" ht="22" customHeight="1">
+      <c r="A16" s="30" t="s">
         <v>11</v>
       </c>
       <c r="B16" s="28"/>
       <c r="C16" s="28"/>
       <c r="D16" s="28"/>
     </row>
-    <row r="17" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="46" t="s">
+    <row r="17" spans="1:4" ht="20" customHeight="1">
+      <c r="A17" s="29" t="s">
         <v>12</v>
       </c>
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
       <c r="D17" s="28"/>
     </row>
-    <row r="18" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="46" t="s">
+    <row r="18" spans="1:4" ht="20" customHeight="1">
+      <c r="A18" s="29" t="s">
         <v>13</v>
       </c>
       <c r="B18" s="28"/>
       <c r="C18" s="28"/>
       <c r="D18" s="28"/>
     </row>
-    <row r="19" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="46" t="s">
+    <row r="19" spans="1:4" ht="20" customHeight="1">
+      <c r="A19" s="29" t="s">
         <v>14</v>
       </c>
       <c r="B19" s="28"/>
       <c r="C19" s="28"/>
       <c r="D19" s="28"/>
     </row>
-    <row r="20" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="46" t="s">
+    <row r="20" spans="1:4" ht="20" customHeight="1">
+      <c r="A20" s="29" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="28"/>
       <c r="C20" s="28"/>
       <c r="D20" s="28"/>
     </row>
-    <row r="21" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="46" t="s">
+    <row r="21" spans="1:4" ht="20" customHeight="1">
+      <c r="A21" s="29" t="s">
         <v>16</v>
       </c>
       <c r="B21" s="28"/>
       <c r="C21" s="28"/>
       <c r="D21" s="28"/>
     </row>
-    <row r="22" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="46" t="s">
+    <row r="22" spans="1:4" ht="20" customHeight="1">
+      <c r="A22" s="29" t="s">
         <v>17</v>
       </c>
       <c r="B22" s="28"/>
       <c r="C22" s="28"/>
       <c r="D22" s="28"/>
     </row>
-    <row r="23" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="46" t="s">
+    <row r="23" spans="1:4" ht="20" customHeight="1">
+      <c r="A23" s="29" t="s">
         <v>18</v>
       </c>
       <c r="B23" s="28"/>
       <c r="C23" s="28"/>
       <c r="D23" s="28"/>
     </row>
-    <row r="24" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="46" t="s">
+    <row r="24" spans="1:4" ht="20" customHeight="1">
+      <c r="A24" s="29" t="s">
         <v>19</v>
       </c>
       <c r="B24" s="28"/>
       <c r="C24" s="28"/>
       <c r="D24" s="28"/>
     </row>
-    <row r="26" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="47" t="s">
+    <row r="26" spans="1:4" ht="22" customHeight="1">
+      <c r="A26" s="30" t="s">
         <v>20</v>
       </c>
       <c r="B26" s="28"/>
       <c r="C26" s="28"/>
       <c r="D26" s="28"/>
     </row>
-    <row r="27" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="46" t="s">
+    <row r="27" spans="1:4" ht="20" customHeight="1">
+      <c r="A27" s="29" t="s">
         <v>21</v>
       </c>
       <c r="B27" s="28"/>
       <c r="C27" s="28"/>
       <c r="D27" s="28"/>
     </row>
-    <row r="29" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="47" t="s">
+    <row r="29" spans="1:4" ht="22" customHeight="1">
+      <c r="A29" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B29" s="28"/>
       <c r="C29" s="28"/>
       <c r="D29" s="28"/>
     </row>
-    <row r="30" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="46" t="s">
+    <row r="30" spans="1:4" ht="20" customHeight="1">
+      <c r="A30" s="29" t="s">
         <v>23</v>
       </c>
       <c r="B30" s="28"/>
       <c r="C30" s="28"/>
       <c r="D30" s="28"/>
     </row>
-    <row r="31" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="46" t="s">
+    <row r="31" spans="1:4" ht="20" customHeight="1">
+      <c r="A31" s="29" t="s">
         <v>24</v>
       </c>
       <c r="B31" s="28"/>
       <c r="C31" s="28"/>
       <c r="D31" s="28"/>
     </row>
-    <row r="33" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="47" t="s">
+    <row r="33" spans="1:4" ht="22" customHeight="1">
+      <c r="A33" s="30" t="s">
         <v>25</v>
       </c>
       <c r="B33" s="28"/>
       <c r="C33" s="28"/>
       <c r="D33" s="28"/>
     </row>
-    <row r="34" spans="1:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="46" t="s">
+    <row r="34" spans="1:4" ht="20" customHeight="1">
+      <c r="A34" s="29" t="s">
         <v>26</v>
       </c>
       <c r="B34" s="28"/>
@@ -2108,7 +2481,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F66"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -2118,8 +2491,8 @@
     <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:6" ht="35" customHeight="1">
+      <c r="A1" s="34" t="s">
         <v>27</v>
       </c>
       <c r="B1" s="28"/>
@@ -2128,7 +2501,7 @@
       <c r="E1" s="28"/>
       <c r="F1" s="28"/>
     </row>
-    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="30" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
@@ -2148,8 +2521,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
+    <row r="3" spans="1:6" ht="25" customHeight="1">
+      <c r="A3" s="41" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="28"/>
@@ -2158,8 +2531,8 @@
       <c r="E3" s="28"/>
       <c r="F3" s="28"/>
     </row>
-    <row r="4" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="33" t="s">
+    <row r="4" spans="1:6" ht="20" customHeight="1">
+      <c r="A4" s="39" t="s">
         <v>35</v>
       </c>
       <c r="B4" s="28"/>
@@ -2168,7 +2541,7 @@
       <c r="E4" s="28"/>
       <c r="F4" s="28"/>
     </row>
-    <row r="5" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="35" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>36</v>
       </c>
@@ -2188,7 +2561,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="97.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="97" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>36</v>
       </c>
@@ -2208,7 +2581,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="50" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>36</v>
       </c>
@@ -2228,7 +2601,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="76.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="77" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>36</v>
       </c>
@@ -2248,7 +2621,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="52" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>36</v>
       </c>
@@ -2268,7 +2641,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="58.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="59" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>36</v>
       </c>
@@ -2288,7 +2661,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="66" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>36</v>
       </c>
@@ -2308,7 +2681,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="51" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>36</v>
       </c>
@@ -2328,7 +2701,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="73.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="73" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
@@ -2348,7 +2721,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="35" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>36</v>
       </c>
@@ -2368,7 +2741,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="47" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>36</v>
       </c>
@@ -2388,7 +2761,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="39" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>36</v>
       </c>
@@ -2408,8 +2781,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="31" t="s">
+    <row r="17" spans="1:6" ht="25" customHeight="1">
+      <c r="A17" s="37" t="s">
         <v>86</v>
       </c>
       <c r="B17" s="28"/>
@@ -2418,8 +2791,8 @@
       <c r="E17" s="28"/>
       <c r="F17" s="28"/>
     </row>
-    <row r="18" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="32" t="s">
+    <row r="18" spans="1:6" ht="20" customHeight="1">
+      <c r="A18" s="38" t="s">
         <v>87</v>
       </c>
       <c r="B18" s="28"/>
@@ -2428,7 +2801,7 @@
       <c r="E18" s="28"/>
       <c r="F18" s="28"/>
     </row>
-    <row r="19" spans="1:6" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="47" customHeight="1">
       <c r="A19" s="8" t="s">
         <v>88</v>
       </c>
@@ -2448,7 +2821,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="75" customHeight="1">
       <c r="A20" s="8" t="s">
         <v>88</v>
       </c>
@@ -2468,7 +2841,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="56" customHeight="1">
       <c r="A21" s="8" t="s">
         <v>88</v>
       </c>
@@ -2488,7 +2861,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="49.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="49" customHeight="1">
       <c r="A22" s="8" t="s">
         <v>88</v>
       </c>
@@ -2508,8 +2881,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="29" t="s">
+    <row r="23" spans="1:6" ht="25" customHeight="1">
+      <c r="A23" s="35" t="s">
         <v>104</v>
       </c>
       <c r="B23" s="28"/>
@@ -2518,8 +2891,8 @@
       <c r="E23" s="28"/>
       <c r="F23" s="28"/>
     </row>
-    <row r="24" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="39" t="s">
+    <row r="24" spans="1:6" ht="20" customHeight="1">
+      <c r="A24" s="45" t="s">
         <v>105</v>
       </c>
       <c r="B24" s="28"/>
@@ -2528,7 +2901,7 @@
       <c r="E24" s="28"/>
       <c r="F24" s="28"/>
     </row>
-    <row r="25" spans="1:6" ht="43.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="43" customHeight="1">
       <c r="A25" s="10" t="s">
         <v>106</v>
       </c>
@@ -2548,7 +2921,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="120" customHeight="1">
       <c r="A26" s="10" t="s">
         <v>106</v>
       </c>
@@ -2568,7 +2941,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="50" customHeight="1">
       <c r="A27" s="10" t="s">
         <v>106</v>
       </c>
@@ -2588,8 +2961,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="44" t="s">
+    <row r="28" spans="1:6" ht="25" customHeight="1">
+      <c r="A28" s="33" t="s">
         <v>119</v>
       </c>
       <c r="B28" s="28"/>
@@ -2598,8 +2971,8 @@
       <c r="E28" s="28"/>
       <c r="F28" s="28"/>
     </row>
-    <row r="29" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="37" t="s">
+    <row r="29" spans="1:6" ht="20" customHeight="1">
+      <c r="A29" s="43" t="s">
         <v>120</v>
       </c>
       <c r="B29" s="28"/>
@@ -2608,7 +2981,7 @@
       <c r="E29" s="28"/>
       <c r="F29" s="28"/>
     </row>
-    <row r="30" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="35" customHeight="1">
       <c r="A30" s="12" t="s">
         <v>121</v>
       </c>
@@ -2628,7 +3001,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="41" customHeight="1">
       <c r="A31" s="12" t="s">
         <v>121</v>
       </c>
@@ -2648,7 +3021,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="36" customHeight="1">
       <c r="A32" s="12" t="s">
         <v>121</v>
       </c>
@@ -2668,7 +3041,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="35" customHeight="1">
       <c r="A33" s="12" t="s">
         <v>121</v>
       </c>
@@ -2688,7 +3061,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="46.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="46" customHeight="1">
       <c r="A34" s="12" t="s">
         <v>121</v>
       </c>
@@ -2708,7 +3081,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="38" customHeight="1">
       <c r="A35" s="12" t="s">
         <v>121</v>
       </c>
@@ -2728,7 +3101,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="35" customHeight="1">
       <c r="A36" s="12" t="s">
         <v>121</v>
       </c>
@@ -2748,7 +3121,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="39" customHeight="1">
       <c r="A37" s="12" t="s">
         <v>121</v>
       </c>
@@ -2768,8 +3141,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="40" t="s">
+    <row r="38" spans="1:6" ht="25" customHeight="1">
+      <c r="A38" s="46" t="s">
         <v>148</v>
       </c>
       <c r="B38" s="28"/>
@@ -2778,8 +3151,8 @@
       <c r="E38" s="28"/>
       <c r="F38" s="28"/>
     </row>
-    <row r="39" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="36" t="s">
+    <row r="39" spans="1:6" ht="20" customHeight="1">
+      <c r="A39" s="42" t="s">
         <v>149</v>
       </c>
       <c r="B39" s="28"/>
@@ -2788,7 +3161,7 @@
       <c r="E39" s="28"/>
       <c r="F39" s="28"/>
     </row>
-    <row r="40" spans="1:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="44" customHeight="1">
       <c r="A40" s="13" t="s">
         <v>150</v>
       </c>
@@ -2808,7 +3181,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="43.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="43" customHeight="1">
       <c r="A41" s="13" t="s">
         <v>150</v>
       </c>
@@ -2828,7 +3201,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="47" customHeight="1">
       <c r="A42" s="13" t="s">
         <v>150</v>
       </c>
@@ -2848,7 +3221,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="57" customHeight="1">
       <c r="A43" s="13" t="s">
         <v>150</v>
       </c>
@@ -2868,7 +3241,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="56" customHeight="1">
       <c r="A44" s="13" t="s">
         <v>150</v>
       </c>
@@ -2888,7 +3261,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="58.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="59" customHeight="1">
       <c r="A45" s="13" t="s">
         <v>150</v>
       </c>
@@ -2908,7 +3281,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="48" customHeight="1">
       <c r="A46" s="13" t="s">
         <v>150</v>
       </c>
@@ -2928,8 +3301,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="43" t="s">
+    <row r="47" spans="1:6" ht="25" customHeight="1">
+      <c r="A47" s="32" t="s">
         <v>172</v>
       </c>
       <c r="B47" s="28"/>
@@ -2938,8 +3311,8 @@
       <c r="E47" s="28"/>
       <c r="F47" s="28"/>
     </row>
-    <row r="48" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="34" t="s">
+    <row r="48" spans="1:6" ht="20" customHeight="1">
+      <c r="A48" s="40" t="s">
         <v>173</v>
       </c>
       <c r="B48" s="28"/>
@@ -2948,7 +3321,7 @@
       <c r="E48" s="28"/>
       <c r="F48" s="28"/>
     </row>
-    <row r="49" spans="1:6" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="38" customHeight="1">
       <c r="A49" s="14" t="s">
         <v>174</v>
       </c>
@@ -2968,7 +3341,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="61.25" customHeight="1">
       <c r="A50" s="14" t="s">
         <v>174</v>
       </c>
@@ -2988,7 +3361,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="54" customHeight="1">
       <c r="A51" s="14" t="s">
         <v>174</v>
       </c>
@@ -3008,7 +3381,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="38" customHeight="1">
       <c r="A52" s="14" t="s">
         <v>174</v>
       </c>
@@ -3028,8 +3401,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="38" t="s">
+    <row r="53" spans="1:6" ht="25" customHeight="1">
+      <c r="A53" s="44" t="s">
         <v>187</v>
       </c>
       <c r="B53" s="28"/>
@@ -3038,8 +3411,8 @@
       <c r="E53" s="28"/>
       <c r="F53" s="28"/>
     </row>
-    <row r="54" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="41" t="s">
+    <row r="54" spans="1:6" ht="20" customHeight="1">
+      <c r="A54" s="47" t="s">
         <v>188</v>
       </c>
       <c r="B54" s="28"/>
@@ -3048,7 +3421,7 @@
       <c r="E54" s="28"/>
       <c r="F54" s="28"/>
     </row>
-    <row r="55" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="35" customHeight="1">
       <c r="A55" s="15" t="s">
         <v>189</v>
       </c>
@@ -3068,7 +3441,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="35" customHeight="1">
       <c r="A56" s="15" t="s">
         <v>189</v>
       </c>
@@ -3088,7 +3461,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="36" customHeight="1">
       <c r="A57" s="15" t="s">
         <v>189</v>
       </c>
@@ -3108,7 +3481,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="41" customHeight="1">
       <c r="A58" s="15" t="s">
         <v>189</v>
       </c>
@@ -3128,7 +3501,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="37.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="37" customHeight="1">
       <c r="A59" s="15" t="s">
         <v>189</v>
       </c>
@@ -3148,7 +3521,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="35" customHeight="1">
       <c r="A60" s="15" t="s">
         <v>189</v>
       </c>
@@ -3168,7 +3541,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="35" customHeight="1">
       <c r="A61" s="15" t="s">
         <v>189</v>
       </c>
@@ -3188,7 +3561,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="49.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="49" customHeight="1">
       <c r="A62" s="15" t="s">
         <v>189</v>
       </c>
@@ -3208,8 +3581,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="42" t="s">
+    <row r="63" spans="1:6" ht="25" customHeight="1">
+      <c r="A63" s="48" t="s">
         <v>217</v>
       </c>
       <c r="B63" s="28"/>
@@ -3218,8 +3591,8 @@
       <c r="E63" s="28"/>
       <c r="F63" s="28"/>
     </row>
-    <row r="64" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="30" t="s">
+    <row r="64" spans="1:6" ht="20" customHeight="1">
+      <c r="A64" s="36" t="s">
         <v>218</v>
       </c>
       <c r="B64" s="28"/>
@@ -3228,7 +3601,7 @@
       <c r="E64" s="28"/>
       <c r="F64" s="28"/>
     </row>
-    <row r="65" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" ht="35" customHeight="1">
       <c r="A65" s="16" t="s">
         <v>219</v>
       </c>
@@ -3248,7 +3621,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" ht="51" customHeight="1">
       <c r="A66" s="16" t="s">
         <v>219</v>
       </c>
@@ -3270,6 +3643,8 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A23:F23"/>
@@ -3285,8 +3660,6 @@
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A63:F63"/>
-    <mergeCell ref="A47:F47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3295,7 +3668,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F66"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -3305,8 +3678,8 @@
     <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:6" ht="35" customHeight="1">
+      <c r="A1" s="49" t="s">
         <v>229</v>
       </c>
       <c r="B1" s="28"/>
@@ -3315,7 +3688,7 @@
       <c r="E1" s="28"/>
       <c r="F1" s="28"/>
     </row>
-    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="30" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
@@ -3335,8 +3708,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
+    <row r="3" spans="1:6" ht="25" customHeight="1">
+      <c r="A3" s="41" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="28"/>
@@ -3345,8 +3718,8 @@
       <c r="E3" s="28"/>
       <c r="F3" s="28"/>
     </row>
-    <row r="4" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="33" t="s">
+    <row r="4" spans="1:6" ht="20" customHeight="1">
+      <c r="A4" s="39" t="s">
         <v>35</v>
       </c>
       <c r="B4" s="28"/>
@@ -3355,7 +3728,7 @@
       <c r="E4" s="28"/>
       <c r="F4" s="28"/>
     </row>
-    <row r="5" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="35" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>36</v>
       </c>
@@ -3375,7 +3748,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="112.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="113" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>36</v>
       </c>
@@ -3395,7 +3768,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="70" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>36</v>
       </c>
@@ -3415,7 +3788,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="70.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="71" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>36</v>
       </c>
@@ -3435,7 +3808,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="52.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="52" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>36</v>
       </c>
@@ -3455,7 +3828,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="63" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>36</v>
       </c>
@@ -3475,7 +3848,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="105" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>36</v>
       </c>
@@ -3495,7 +3868,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="118.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="118" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>36</v>
       </c>
@@ -3515,7 +3888,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="76.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="77" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
@@ -3535,7 +3908,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="45" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>36</v>
       </c>
@@ -3555,7 +3928,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="36" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>36</v>
       </c>
@@ -3575,7 +3948,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="50" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>36</v>
       </c>
@@ -3595,8 +3968,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="31" t="s">
+    <row r="17" spans="1:6" ht="25" customHeight="1">
+      <c r="A17" s="37" t="s">
         <v>86</v>
       </c>
       <c r="B17" s="28"/>
@@ -3605,8 +3978,8 @@
       <c r="E17" s="28"/>
       <c r="F17" s="28"/>
     </row>
-    <row r="18" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="32" t="s">
+    <row r="18" spans="1:6" ht="20" customHeight="1">
+      <c r="A18" s="38" t="s">
         <v>87</v>
       </c>
       <c r="B18" s="28"/>
@@ -3615,7 +3988,7 @@
       <c r="E18" s="28"/>
       <c r="F18" s="28"/>
     </row>
-    <row r="19" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="51" customHeight="1">
       <c r="A19" s="8" t="s">
         <v>88</v>
       </c>
@@ -3635,7 +4008,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="71.5" customHeight="1">
       <c r="A20" s="8" t="s">
         <v>88</v>
       </c>
@@ -3655,7 +4028,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="120" customHeight="1">
       <c r="A21" s="8" t="s">
         <v>88</v>
       </c>
@@ -3675,7 +4048,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="62" customHeight="1">
       <c r="A22" s="8" t="s">
         <v>88</v>
       </c>
@@ -3695,8 +4068,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="29" t="s">
+    <row r="23" spans="1:6" ht="25" customHeight="1">
+      <c r="A23" s="35" t="s">
         <v>104</v>
       </c>
       <c r="B23" s="28"/>
@@ -3705,8 +4078,8 @@
       <c r="E23" s="28"/>
       <c r="F23" s="28"/>
     </row>
-    <row r="24" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="39" t="s">
+    <row r="24" spans="1:6" ht="20" customHeight="1">
+      <c r="A24" s="45" t="s">
         <v>105</v>
       </c>
       <c r="B24" s="28"/>
@@ -3715,7 +4088,7 @@
       <c r="E24" s="28"/>
       <c r="F24" s="28"/>
     </row>
-    <row r="25" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="120" customHeight="1">
       <c r="A25" s="10" t="s">
         <v>106</v>
       </c>
@@ -3735,7 +4108,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="120" customHeight="1">
       <c r="A26" s="10" t="s">
         <v>106</v>
       </c>
@@ -3755,7 +4128,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="120" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="120" customHeight="1">
       <c r="A27" s="10" t="s">
         <v>106</v>
       </c>
@@ -3775,8 +4148,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="44" t="s">
+    <row r="28" spans="1:6" ht="25" customHeight="1">
+      <c r="A28" s="33" t="s">
         <v>119</v>
       </c>
       <c r="B28" s="28"/>
@@ -3785,8 +4158,8 @@
       <c r="E28" s="28"/>
       <c r="F28" s="28"/>
     </row>
-    <row r="29" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="37" t="s">
+    <row r="29" spans="1:6" ht="20" customHeight="1">
+      <c r="A29" s="43" t="s">
         <v>120</v>
       </c>
       <c r="B29" s="28"/>
@@ -3795,7 +4168,7 @@
       <c r="E29" s="28"/>
       <c r="F29" s="28"/>
     </row>
-    <row r="30" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="35" customHeight="1">
       <c r="A30" s="12" t="s">
         <v>121</v>
       </c>
@@ -3815,7 +4188,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="35" customHeight="1">
       <c r="A31" s="12" t="s">
         <v>121</v>
       </c>
@@ -3835,7 +4208,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="35" customHeight="1">
       <c r="A32" s="12" t="s">
         <v>121</v>
       </c>
@@ -3855,7 +4228,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="35" customHeight="1">
       <c r="A33" s="12" t="s">
         <v>121</v>
       </c>
@@ -3875,7 +4248,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="40" customHeight="1">
       <c r="A34" s="12" t="s">
         <v>121</v>
       </c>
@@ -3895,7 +4268,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="45" customHeight="1">
       <c r="A35" s="12" t="s">
         <v>121</v>
       </c>
@@ -3915,7 +4288,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="35" customHeight="1">
       <c r="A36" s="12" t="s">
         <v>121</v>
       </c>
@@ -3935,7 +4308,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="35" customHeight="1">
       <c r="A37" s="12" t="s">
         <v>121</v>
       </c>
@@ -3955,8 +4328,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="40" t="s">
+    <row r="38" spans="1:6" ht="25" customHeight="1">
+      <c r="A38" s="46" t="s">
         <v>148</v>
       </c>
       <c r="B38" s="28"/>
@@ -3965,8 +4338,8 @@
       <c r="E38" s="28"/>
       <c r="F38" s="28"/>
     </row>
-    <row r="39" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="36" t="s">
+    <row r="39" spans="1:6" ht="20" customHeight="1">
+      <c r="A39" s="42" t="s">
         <v>149</v>
       </c>
       <c r="B39" s="28"/>
@@ -3975,7 +4348,7 @@
       <c r="E39" s="28"/>
       <c r="F39" s="28"/>
     </row>
-    <row r="40" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="35" customHeight="1">
       <c r="A40" s="13" t="s">
         <v>150</v>
       </c>
@@ -3995,7 +4368,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="47" customHeight="1">
       <c r="A41" s="13" t="s">
         <v>150</v>
       </c>
@@ -4015,7 +4388,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="48" customHeight="1">
       <c r="A42" s="13" t="s">
         <v>150</v>
       </c>
@@ -4035,7 +4408,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="56" customHeight="1">
       <c r="A43" s="13" t="s">
         <v>150</v>
       </c>
@@ -4055,7 +4428,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="58" customHeight="1">
       <c r="A44" s="13" t="s">
         <v>150</v>
       </c>
@@ -4075,7 +4448,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="64" customHeight="1">
       <c r="A45" s="13" t="s">
         <v>150</v>
       </c>
@@ -4095,7 +4468,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="46.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="47" customHeight="1">
       <c r="A46" s="13" t="s">
         <v>150</v>
       </c>
@@ -4115,8 +4488,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="43" t="s">
+    <row r="47" spans="1:6" ht="25" customHeight="1">
+      <c r="A47" s="32" t="s">
         <v>172</v>
       </c>
       <c r="B47" s="28"/>
@@ -4125,8 +4498,8 @@
       <c r="E47" s="28"/>
       <c r="F47" s="28"/>
     </row>
-    <row r="48" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="34" t="s">
+    <row r="48" spans="1:6" ht="20" customHeight="1">
+      <c r="A48" s="40" t="s">
         <v>173</v>
       </c>
       <c r="B48" s="28"/>
@@ -4135,7 +4508,7 @@
       <c r="E48" s="28"/>
       <c r="F48" s="28"/>
     </row>
-    <row r="49" spans="1:6" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="38" customHeight="1">
       <c r="A49" s="14" t="s">
         <v>174</v>
       </c>
@@ -4155,7 +4528,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="50" customHeight="1">
       <c r="A50" s="14" t="s">
         <v>174</v>
       </c>
@@ -4175,7 +4548,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="57" customHeight="1">
       <c r="A51" s="14" t="s">
         <v>174</v>
       </c>
@@ -4195,7 +4568,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="36" customHeight="1">
       <c r="A52" s="14" t="s">
         <v>174</v>
       </c>
@@ -4215,8 +4588,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="38" t="s">
+    <row r="53" spans="1:6" ht="25" customHeight="1">
+      <c r="A53" s="44" t="s">
         <v>187</v>
       </c>
       <c r="B53" s="28"/>
@@ -4225,8 +4598,8 @@
       <c r="E53" s="28"/>
       <c r="F53" s="28"/>
     </row>
-    <row r="54" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="41" t="s">
+    <row r="54" spans="1:6" ht="20" customHeight="1">
+      <c r="A54" s="47" t="s">
         <v>188</v>
       </c>
       <c r="B54" s="28"/>
@@ -4235,7 +4608,7 @@
       <c r="E54" s="28"/>
       <c r="F54" s="28"/>
     </row>
-    <row r="55" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="35" customHeight="1">
       <c r="A55" s="15" t="s">
         <v>189</v>
       </c>
@@ -4255,7 +4628,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="35" customHeight="1">
       <c r="A56" s="15" t="s">
         <v>189</v>
       </c>
@@ -4275,7 +4648,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="36" customHeight="1">
       <c r="A57" s="15" t="s">
         <v>189</v>
       </c>
@@ -4295,7 +4668,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="35" customHeight="1">
       <c r="A58" s="15" t="s">
         <v>189</v>
       </c>
@@ -4315,7 +4688,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="37.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="37" customHeight="1">
       <c r="A59" s="15" t="s">
         <v>189</v>
       </c>
@@ -4335,7 +4708,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="35" customHeight="1">
       <c r="A60" s="15" t="s">
         <v>189</v>
       </c>
@@ -4355,7 +4728,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="35" customHeight="1">
       <c r="A61" s="15" t="s">
         <v>189</v>
       </c>
@@ -4375,7 +4748,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="45" customHeight="1">
       <c r="A62" s="15" t="s">
         <v>189</v>
       </c>
@@ -4395,8 +4768,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="42" t="s">
+    <row r="63" spans="1:6" ht="25" customHeight="1">
+      <c r="A63" s="48" t="s">
         <v>217</v>
       </c>
       <c r="B63" s="28"/>
@@ -4405,8 +4778,8 @@
       <c r="E63" s="28"/>
       <c r="F63" s="28"/>
     </row>
-    <row r="64" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="30" t="s">
+    <row r="64" spans="1:6" ht="20" customHeight="1">
+      <c r="A64" s="36" t="s">
         <v>218</v>
       </c>
       <c r="B64" s="28"/>
@@ -4415,7 +4788,7 @@
       <c r="E64" s="28"/>
       <c r="F64" s="28"/>
     </row>
-    <row r="65" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" ht="35" customHeight="1">
       <c r="A65" s="16" t="s">
         <v>219</v>
       </c>
@@ -4435,7 +4808,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="85.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" ht="85" customHeight="1">
       <c r="A66" s="16" t="s">
         <v>219</v>
       </c>
@@ -4457,6 +4830,8 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A23:F23"/>
@@ -4472,8 +4847,6 @@
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A63:F63"/>
-    <mergeCell ref="A47:F47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4482,7 +4855,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F66"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -4492,8 +4865,8 @@
     <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:6" ht="35" customHeight="1">
+      <c r="A1" s="34" t="s">
         <v>252</v>
       </c>
       <c r="B1" s="28"/>
@@ -4502,7 +4875,7 @@
       <c r="E1" s="28"/>
       <c r="F1" s="28"/>
     </row>
-    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="30" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
@@ -4522,8 +4895,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
+    <row r="3" spans="1:6" ht="25" customHeight="1">
+      <c r="A3" s="41" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="28"/>
@@ -4532,8 +4905,8 @@
       <c r="E3" s="28"/>
       <c r="F3" s="28"/>
     </row>
-    <row r="4" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="33" t="s">
+    <row r="4" spans="1:6" ht="20" customHeight="1">
+      <c r="A4" s="39" t="s">
         <v>35</v>
       </c>
       <c r="B4" s="28"/>
@@ -4542,7 +4915,7 @@
       <c r="E4" s="28"/>
       <c r="F4" s="28"/>
     </row>
-    <row r="5" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="35" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>36</v>
       </c>
@@ -4560,7 +4933,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="40" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>36</v>
       </c>
@@ -4578,7 +4951,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="42" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>36</v>
       </c>
@@ -4596,7 +4969,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="38" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>36</v>
       </c>
@@ -4614,7 +4987,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="35" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>36</v>
       </c>
@@ -4632,7 +5005,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="35" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>36</v>
       </c>
@@ -4650,7 +5023,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="35" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>36</v>
       </c>
@@ -4668,7 +5041,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="36" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>36</v>
       </c>
@@ -4686,7 +5059,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="37.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="37" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
@@ -4704,7 +5077,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="35" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>36</v>
       </c>
@@ -4722,7 +5095,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="36" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>36</v>
       </c>
@@ -4740,7 +5113,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="35" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>36</v>
       </c>
@@ -4758,8 +5131,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="31" t="s">
+    <row r="17" spans="1:6" ht="25" customHeight="1">
+      <c r="A17" s="37" t="s">
         <v>86</v>
       </c>
       <c r="B17" s="28"/>
@@ -4768,8 +5141,8 @@
       <c r="E17" s="28"/>
       <c r="F17" s="28"/>
     </row>
-    <row r="18" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="32" t="s">
+    <row r="18" spans="1:6" ht="20" customHeight="1">
+      <c r="A18" s="38" t="s">
         <v>87</v>
       </c>
       <c r="B18" s="28"/>
@@ -4778,7 +5151,7 @@
       <c r="E18" s="28"/>
       <c r="F18" s="28"/>
     </row>
-    <row r="19" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="35" customHeight="1">
       <c r="A19" s="8" t="s">
         <v>88</v>
       </c>
@@ -4796,7 +5169,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="37.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="37" customHeight="1">
       <c r="A20" s="8" t="s">
         <v>88</v>
       </c>
@@ -4814,7 +5187,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="36" customHeight="1">
       <c r="A21" s="8" t="s">
         <v>88</v>
       </c>
@@ -4832,7 +5205,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="36" customHeight="1">
       <c r="A22" s="8" t="s">
         <v>88</v>
       </c>
@@ -4850,8 +5223,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="29" t="s">
+    <row r="23" spans="1:6" ht="25" customHeight="1">
+      <c r="A23" s="35" t="s">
         <v>104</v>
       </c>
       <c r="B23" s="28"/>
@@ -4860,8 +5233,8 @@
       <c r="E23" s="28"/>
       <c r="F23" s="28"/>
     </row>
-    <row r="24" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="39" t="s">
+    <row r="24" spans="1:6" ht="20" customHeight="1">
+      <c r="A24" s="45" t="s">
         <v>105</v>
       </c>
       <c r="B24" s="28"/>
@@ -4870,7 +5243,7 @@
       <c r="E24" s="28"/>
       <c r="F24" s="28"/>
     </row>
-    <row r="25" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="36" customHeight="1">
       <c r="A25" s="10" t="s">
         <v>106</v>
       </c>
@@ -4888,7 +5261,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="36" customHeight="1">
       <c r="A26" s="10" t="s">
         <v>106</v>
       </c>
@@ -4906,7 +5279,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="38" customHeight="1">
       <c r="A27" s="10" t="s">
         <v>106</v>
       </c>
@@ -4924,8 +5297,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="44" t="s">
+    <row r="28" spans="1:6" ht="25" customHeight="1">
+      <c r="A28" s="33" t="s">
         <v>119</v>
       </c>
       <c r="B28" s="28"/>
@@ -4934,8 +5307,8 @@
       <c r="E28" s="28"/>
       <c r="F28" s="28"/>
     </row>
-    <row r="29" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="37" t="s">
+    <row r="29" spans="1:6" ht="20" customHeight="1">
+      <c r="A29" s="43" t="s">
         <v>120</v>
       </c>
       <c r="B29" s="28"/>
@@ -4944,7 +5317,7 @@
       <c r="E29" s="28"/>
       <c r="F29" s="28"/>
     </row>
-    <row r="30" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="35" customHeight="1">
       <c r="A30" s="12" t="s">
         <v>121</v>
       </c>
@@ -4962,7 +5335,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="35" customHeight="1">
       <c r="A31" s="12" t="s">
         <v>121</v>
       </c>
@@ -4980,7 +5353,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="35" customHeight="1">
       <c r="A32" s="12" t="s">
         <v>121</v>
       </c>
@@ -4998,7 +5371,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="35" customHeight="1">
       <c r="A33" s="12" t="s">
         <v>121</v>
       </c>
@@ -5016,7 +5389,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="35" customHeight="1">
       <c r="A34" s="12" t="s">
         <v>121</v>
       </c>
@@ -5034,7 +5407,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="35" customHeight="1">
       <c r="A35" s="12" t="s">
         <v>121</v>
       </c>
@@ -5052,7 +5425,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="35" customHeight="1">
       <c r="A36" s="12" t="s">
         <v>121</v>
       </c>
@@ -5070,7 +5443,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="35" customHeight="1">
       <c r="A37" s="12" t="s">
         <v>121</v>
       </c>
@@ -5088,8 +5461,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="40" t="s">
+    <row r="38" spans="1:6" ht="25" customHeight="1">
+      <c r="A38" s="46" t="s">
         <v>148</v>
       </c>
       <c r="B38" s="28"/>
@@ -5098,8 +5471,8 @@
       <c r="E38" s="28"/>
       <c r="F38" s="28"/>
     </row>
-    <row r="39" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="36" t="s">
+    <row r="39" spans="1:6" ht="20" customHeight="1">
+      <c r="A39" s="42" t="s">
         <v>149</v>
       </c>
       <c r="B39" s="28"/>
@@ -5108,7 +5481,7 @@
       <c r="E39" s="28"/>
       <c r="F39" s="28"/>
     </row>
-    <row r="40" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="35" customHeight="1">
       <c r="A40" s="13" t="s">
         <v>150</v>
       </c>
@@ -5126,7 +5499,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="37.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="37" customHeight="1">
       <c r="A41" s="13" t="s">
         <v>150</v>
       </c>
@@ -5144,7 +5517,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="35" customHeight="1">
       <c r="A42" s="13" t="s">
         <v>150</v>
       </c>
@@ -5162,7 +5535,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="36" customHeight="1">
       <c r="A43" s="13" t="s">
         <v>150</v>
       </c>
@@ -5180,7 +5553,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="44" customHeight="1">
       <c r="A44" s="13" t="s">
         <v>150</v>
       </c>
@@ -5198,7 +5571,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="35" customHeight="1">
       <c r="A45" s="13" t="s">
         <v>150</v>
       </c>
@@ -5216,7 +5589,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="39" customHeight="1">
       <c r="A46" s="13" t="s">
         <v>150</v>
       </c>
@@ -5234,8 +5607,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="43" t="s">
+    <row r="47" spans="1:6" ht="25" customHeight="1">
+      <c r="A47" s="32" t="s">
         <v>172</v>
       </c>
       <c r="B47" s="28"/>
@@ -5244,8 +5617,8 @@
       <c r="E47" s="28"/>
       <c r="F47" s="28"/>
     </row>
-    <row r="48" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="34" t="s">
+    <row r="48" spans="1:6" ht="20" customHeight="1">
+      <c r="A48" s="40" t="s">
         <v>173</v>
       </c>
       <c r="B48" s="28"/>
@@ -5254,7 +5627,7 @@
       <c r="E48" s="28"/>
       <c r="F48" s="28"/>
     </row>
-    <row r="49" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="35" customHeight="1">
       <c r="A49" s="14" t="s">
         <v>174</v>
       </c>
@@ -5272,7 +5645,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="35" customHeight="1">
       <c r="A50" s="14" t="s">
         <v>174</v>
       </c>
@@ -5290,7 +5663,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="35" customHeight="1">
       <c r="A51" s="14" t="s">
         <v>174</v>
       </c>
@@ -5308,7 +5681,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="36" customHeight="1">
       <c r="A52" s="14" t="s">
         <v>174</v>
       </c>
@@ -5326,8 +5699,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="38" t="s">
+    <row r="53" spans="1:6" ht="25" customHeight="1">
+      <c r="A53" s="44" t="s">
         <v>187</v>
       </c>
       <c r="B53" s="28"/>
@@ -5336,8 +5709,8 @@
       <c r="E53" s="28"/>
       <c r="F53" s="28"/>
     </row>
-    <row r="54" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="41" t="s">
+    <row r="54" spans="1:6" ht="20" customHeight="1">
+      <c r="A54" s="47" t="s">
         <v>188</v>
       </c>
       <c r="B54" s="28"/>
@@ -5346,7 +5719,7 @@
       <c r="E54" s="28"/>
       <c r="F54" s="28"/>
     </row>
-    <row r="55" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="35" customHeight="1">
       <c r="A55" s="15" t="s">
         <v>189</v>
       </c>
@@ -5364,7 +5737,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="35" customHeight="1">
       <c r="A56" s="15" t="s">
         <v>189</v>
       </c>
@@ -5382,7 +5755,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="36" customHeight="1">
       <c r="A57" s="15" t="s">
         <v>189</v>
       </c>
@@ -5400,7 +5773,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="35" customHeight="1">
       <c r="A58" s="15" t="s">
         <v>189</v>
       </c>
@@ -5418,7 +5791,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="37.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="37" customHeight="1">
       <c r="A59" s="15" t="s">
         <v>189</v>
       </c>
@@ -5436,7 +5809,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="35" customHeight="1">
       <c r="A60" s="15" t="s">
         <v>189</v>
       </c>
@@ -5454,7 +5827,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="35" customHeight="1">
       <c r="A61" s="15" t="s">
         <v>189</v>
       </c>
@@ -5472,7 +5845,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="36" customHeight="1">
       <c r="A62" s="15" t="s">
         <v>189</v>
       </c>
@@ -5490,8 +5863,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="42" t="s">
+    <row r="63" spans="1:6" ht="25" customHeight="1">
+      <c r="A63" s="48" t="s">
         <v>217</v>
       </c>
       <c r="B63" s="28"/>
@@ -5500,8 +5873,8 @@
       <c r="E63" s="28"/>
       <c r="F63" s="28"/>
     </row>
-    <row r="64" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="30" t="s">
+    <row r="64" spans="1:6" ht="20" customHeight="1">
+      <c r="A64" s="36" t="s">
         <v>218</v>
       </c>
       <c r="B64" s="28"/>
@@ -5510,7 +5883,7 @@
       <c r="E64" s="28"/>
       <c r="F64" s="28"/>
     </row>
-    <row r="65" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" ht="35" customHeight="1">
       <c r="A65" s="16" t="s">
         <v>219</v>
       </c>
@@ -5528,7 +5901,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" ht="35" customHeight="1">
       <c r="A66" s="16" t="s">
         <v>219</v>
       </c>
@@ -5548,6 +5921,8 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A23:F23"/>
@@ -5563,17 +5938,3991 @@
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A63:F63"/>
-    <mergeCell ref="A47:F47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1D75AD9-018D-3746-A99B-E66884519DFC}">
+  <dimension ref="A1:F1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="5" width="70.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.1640625" customWidth="1"/>
+    <col min="7" max="26" width="8.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A1" s="51" t="s">
+        <v>416</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+    </row>
+    <row r="2" spans="1:6" ht="30" customHeight="1">
+      <c r="A2" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="53" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="24.75" customHeight="1">
+      <c r="A3" s="54" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+    </row>
+    <row r="4" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A4" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+    </row>
+    <row r="5" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A5" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="57" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="60" t="s">
+        <v>375</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="91.5" customHeight="1">
+      <c r="A6" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="57" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="58" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="61" t="s">
+        <v>376</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="67.5" customHeight="1">
+      <c r="A7" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="57" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="58" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="59" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="61" t="s">
+        <v>377</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="93.75" customHeight="1">
+      <c r="A8" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="59" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="61" t="s">
+        <v>378</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A9" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="57" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="58" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="59" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="61" t="s">
+        <v>379</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="61.5" customHeight="1">
+      <c r="A10" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="59" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="61" t="s">
+        <v>380</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="58.5" customHeight="1">
+      <c r="A11" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="57" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="58" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="59" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="61" t="s">
+        <v>381</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="83.25" customHeight="1">
+      <c r="A12" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="57" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="59" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="61" t="s">
+        <v>382</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="36.75" customHeight="1">
+      <c r="A13" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="57" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="58" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="59" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="61" t="s">
+        <v>383</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A14" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="57" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="58" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="59" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="61" t="s">
+        <v>384</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="36" customHeight="1">
+      <c r="A15" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="57" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="59" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="61" t="s">
+        <v>385</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="56.25" customHeight="1">
+      <c r="A16" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="57" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="59" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="61" t="s">
+        <v>386</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="24.75" customHeight="1">
+      <c r="A17" s="62" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+    </row>
+    <row r="18" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A18" s="63" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="52"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
+    </row>
+    <row r="19" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A19" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="57" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="58" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" s="61"/>
+      <c r="F19" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="88.5" customHeight="1">
+      <c r="A20" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="E20" s="61" t="s">
+        <v>387</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="52.5" customHeight="1">
+      <c r="A21" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" s="57" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="58" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="61" t="s">
+        <v>388</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="36" customHeight="1">
+      <c r="A22" s="64" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="57" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" s="58" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" s="59" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" s="61" t="s">
+        <v>389</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="24.75" customHeight="1">
+      <c r="A23" s="65" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="52"/>
+    </row>
+    <row r="24" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A24" s="66" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" s="52"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="52"/>
+    </row>
+    <row r="25" spans="1:6" ht="36" customHeight="1">
+      <c r="A25" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" s="58" t="s">
+        <v>108</v>
+      </c>
+      <c r="D25" s="59" t="s">
+        <v>109</v>
+      </c>
+      <c r="E25" s="61" t="s">
+        <v>390</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="36" customHeight="1">
+      <c r="A26" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="B26" s="57" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="D26" s="59" t="s">
+        <v>113</v>
+      </c>
+      <c r="E26" s="61" t="s">
+        <v>391</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="37.5" customHeight="1">
+      <c r="A27" s="67" t="s">
+        <v>106</v>
+      </c>
+      <c r="B27" s="57" t="s">
+        <v>115</v>
+      </c>
+      <c r="C27" s="58" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="E27" s="61" t="s">
+        <v>392</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="24.75" customHeight="1">
+      <c r="A28" s="68" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" s="52"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="52"/>
+    </row>
+    <row r="29" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A29" s="69" t="s">
+        <v>120</v>
+      </c>
+      <c r="B29" s="52"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="52"/>
+    </row>
+    <row r="30" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A30" s="70" t="s">
+        <v>121</v>
+      </c>
+      <c r="B30" s="57" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="D30" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="E30" s="61"/>
+      <c r="F30" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A31" s="70" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" s="57" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" s="58" t="s">
+        <v>127</v>
+      </c>
+      <c r="D31" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E31" s="61"/>
+      <c r="F31" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A32" s="70" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="E32" s="61" t="s">
+        <v>393</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A33" s="70" t="s">
+        <v>121</v>
+      </c>
+      <c r="B33" s="57" t="s">
+        <v>133</v>
+      </c>
+      <c r="C33" s="58" t="s">
+        <v>134</v>
+      </c>
+      <c r="D33" s="59" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33" s="61" t="s">
+        <v>394</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A34" s="70" t="s">
+        <v>121</v>
+      </c>
+      <c r="B34" s="57" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34" s="58" t="s">
+        <v>137</v>
+      </c>
+      <c r="D34" s="59" t="s">
+        <v>138</v>
+      </c>
+      <c r="E34" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A35" s="70" t="s">
+        <v>121</v>
+      </c>
+      <c r="B35" s="57" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" s="58" t="s">
+        <v>140</v>
+      </c>
+      <c r="D35" s="59" t="s">
+        <v>141</v>
+      </c>
+      <c r="E35" s="61" t="s">
+        <v>396</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A36" s="70" t="s">
+        <v>121</v>
+      </c>
+      <c r="B36" s="57" t="s">
+        <v>142</v>
+      </c>
+      <c r="C36" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="D36" s="59" t="s">
+        <v>144</v>
+      </c>
+      <c r="E36" s="61" t="s">
+        <v>397</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A37" s="70" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" s="57" t="s">
+        <v>145</v>
+      </c>
+      <c r="C37" s="58" t="s">
+        <v>146</v>
+      </c>
+      <c r="D37" s="59" t="s">
+        <v>147</v>
+      </c>
+      <c r="E37" s="61" t="s">
+        <v>398</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="24.75" customHeight="1">
+      <c r="A38" s="71" t="s">
+        <v>148</v>
+      </c>
+      <c r="B38" s="52"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+    </row>
+    <row r="39" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A39" s="72" t="s">
+        <v>149</v>
+      </c>
+      <c r="B39" s="52"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
+    </row>
+    <row r="40" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A40" s="73" t="s">
+        <v>150</v>
+      </c>
+      <c r="B40" s="57" t="s">
+        <v>151</v>
+      </c>
+      <c r="C40" s="58" t="s">
+        <v>152</v>
+      </c>
+      <c r="D40" s="59" t="s">
+        <v>153</v>
+      </c>
+      <c r="E40" s="61" t="s">
+        <v>399</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="36.75" customHeight="1">
+      <c r="A41" s="73" t="s">
+        <v>150</v>
+      </c>
+      <c r="B41" s="57" t="s">
+        <v>154</v>
+      </c>
+      <c r="C41" s="58" t="s">
+        <v>155</v>
+      </c>
+      <c r="D41" s="59" t="s">
+        <v>156</v>
+      </c>
+      <c r="E41" s="61" t="s">
+        <v>400</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A42" s="73" t="s">
+        <v>150</v>
+      </c>
+      <c r="B42" s="57" t="s">
+        <v>157</v>
+      </c>
+      <c r="C42" s="58" t="s">
+        <v>158</v>
+      </c>
+      <c r="D42" s="59" t="s">
+        <v>159</v>
+      </c>
+      <c r="E42" s="74" t="s">
+        <v>401</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="36" customHeight="1">
+      <c r="A43" s="73" t="s">
+        <v>150</v>
+      </c>
+      <c r="B43" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="C43" s="58" t="s">
+        <v>161</v>
+      </c>
+      <c r="D43" s="59" t="s">
+        <v>162</v>
+      </c>
+      <c r="E43" s="60" t="s">
+        <v>402</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="43.5" customHeight="1">
+      <c r="A44" s="73" t="s">
+        <v>150</v>
+      </c>
+      <c r="B44" s="57" t="s">
+        <v>163</v>
+      </c>
+      <c r="C44" s="58" t="s">
+        <v>164</v>
+      </c>
+      <c r="D44" s="59" t="s">
+        <v>165</v>
+      </c>
+      <c r="E44" s="61" t="s">
+        <v>403</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A45" s="73" t="s">
+        <v>150</v>
+      </c>
+      <c r="B45" s="57" t="s">
+        <v>166</v>
+      </c>
+      <c r="C45" s="58" t="s">
+        <v>167</v>
+      </c>
+      <c r="D45" s="59" t="s">
+        <v>168</v>
+      </c>
+      <c r="E45" s="61" t="s">
+        <v>404</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="39" customHeight="1">
+      <c r="A46" s="73" t="s">
+        <v>150</v>
+      </c>
+      <c r="B46" s="57" t="s">
+        <v>169</v>
+      </c>
+      <c r="C46" s="58" t="s">
+        <v>170</v>
+      </c>
+      <c r="D46" s="59" t="s">
+        <v>171</v>
+      </c>
+      <c r="E46" s="61" t="s">
+        <v>405</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="24.75" customHeight="1">
+      <c r="A47" s="75" t="s">
+        <v>172</v>
+      </c>
+      <c r="B47" s="52"/>
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+    </row>
+    <row r="48" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A48" s="76" t="s">
+        <v>173</v>
+      </c>
+      <c r="B48" s="52"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+    </row>
+    <row r="49" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A49" s="77" t="s">
+        <v>174</v>
+      </c>
+      <c r="B49" s="57" t="s">
+        <v>175</v>
+      </c>
+      <c r="C49" s="58" t="s">
+        <v>176</v>
+      </c>
+      <c r="D49" s="59" t="s">
+        <v>177</v>
+      </c>
+      <c r="E49" s="61" t="s">
+        <v>406</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A50" s="77" t="s">
+        <v>174</v>
+      </c>
+      <c r="B50" s="57" t="s">
+        <v>178</v>
+      </c>
+      <c r="C50" s="58" t="s">
+        <v>179</v>
+      </c>
+      <c r="D50" s="59" t="s">
+        <v>180</v>
+      </c>
+      <c r="E50" s="61" t="s">
+        <v>407</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A51" s="77" t="s">
+        <v>174</v>
+      </c>
+      <c r="B51" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="C51" s="58" t="s">
+        <v>182</v>
+      </c>
+      <c r="D51" s="59" t="s">
+        <v>183</v>
+      </c>
+      <c r="E51" s="61" t="s">
+        <v>408</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="36" customHeight="1">
+      <c r="A52" s="77" t="s">
+        <v>174</v>
+      </c>
+      <c r="B52" s="57" t="s">
+        <v>184</v>
+      </c>
+      <c r="C52" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="D52" s="59" t="s">
+        <v>186</v>
+      </c>
+      <c r="E52" s="61" t="s">
+        <v>409</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="24.75" customHeight="1">
+      <c r="A53" s="78" t="s">
+        <v>187</v>
+      </c>
+      <c r="B53" s="52"/>
+      <c r="C53" s="52"/>
+      <c r="D53" s="52"/>
+      <c r="E53" s="52"/>
+      <c r="F53" s="52"/>
+    </row>
+    <row r="54" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A54" s="79" t="s">
+        <v>188</v>
+      </c>
+      <c r="B54" s="52"/>
+      <c r="C54" s="52"/>
+      <c r="D54" s="52"/>
+      <c r="E54" s="52"/>
+      <c r="F54" s="52"/>
+    </row>
+    <row r="55" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A55" s="80" t="s">
+        <v>189</v>
+      </c>
+      <c r="B55" s="57" t="s">
+        <v>190</v>
+      </c>
+      <c r="C55" s="58" t="s">
+        <v>191</v>
+      </c>
+      <c r="D55" s="59" t="s">
+        <v>192</v>
+      </c>
+      <c r="E55" s="61"/>
+      <c r="F55" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A56" s="80" t="s">
+        <v>189</v>
+      </c>
+      <c r="B56" s="57" t="s">
+        <v>194</v>
+      </c>
+      <c r="C56" s="58" t="s">
+        <v>195</v>
+      </c>
+      <c r="D56" s="59" t="s">
+        <v>196</v>
+      </c>
+      <c r="E56" s="61"/>
+      <c r="F56" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="36" customHeight="1">
+      <c r="A57" s="80" t="s">
+        <v>189</v>
+      </c>
+      <c r="B57" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="C57" s="58" t="s">
+        <v>199</v>
+      </c>
+      <c r="D57" s="59" t="s">
+        <v>200</v>
+      </c>
+      <c r="E57" s="61"/>
+      <c r="F57" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A58" s="80" t="s">
+        <v>189</v>
+      </c>
+      <c r="B58" s="57" t="s">
+        <v>202</v>
+      </c>
+      <c r="C58" s="58" t="s">
+        <v>203</v>
+      </c>
+      <c r="D58" s="59" t="s">
+        <v>204</v>
+      </c>
+      <c r="E58" s="61" t="s">
+        <v>410</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="36.75" customHeight="1">
+      <c r="A59" s="80" t="s">
+        <v>189</v>
+      </c>
+      <c r="B59" s="57" t="s">
+        <v>205</v>
+      </c>
+      <c r="C59" s="58" t="s">
+        <v>206</v>
+      </c>
+      <c r="D59" s="59" t="s">
+        <v>207</v>
+      </c>
+      <c r="E59" s="61" t="s">
+        <v>411</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A60" s="80" t="s">
+        <v>189</v>
+      </c>
+      <c r="B60" s="57" t="s">
+        <v>208</v>
+      </c>
+      <c r="C60" s="58" t="s">
+        <v>209</v>
+      </c>
+      <c r="D60" s="59" t="s">
+        <v>210</v>
+      </c>
+      <c r="E60" s="61" t="s">
+        <v>412</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A61" s="80" t="s">
+        <v>189</v>
+      </c>
+      <c r="B61" s="57" t="s">
+        <v>211</v>
+      </c>
+      <c r="C61" s="58" t="s">
+        <v>212</v>
+      </c>
+      <c r="D61" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="E61" s="61" t="s">
+        <v>413</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="36" customHeight="1">
+      <c r="A62" s="80" t="s">
+        <v>189</v>
+      </c>
+      <c r="B62" s="57" t="s">
+        <v>214</v>
+      </c>
+      <c r="C62" s="58" t="s">
+        <v>215</v>
+      </c>
+      <c r="D62" s="59" t="s">
+        <v>216</v>
+      </c>
+      <c r="E62" s="61" t="s">
+        <v>414</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="24.75" customHeight="1">
+      <c r="A63" s="81" t="s">
+        <v>217</v>
+      </c>
+      <c r="B63" s="52"/>
+      <c r="C63" s="52"/>
+      <c r="D63" s="52"/>
+      <c r="E63" s="52"/>
+      <c r="F63" s="52"/>
+    </row>
+    <row r="64" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A64" s="82" t="s">
+        <v>218</v>
+      </c>
+      <c r="B64" s="52"/>
+      <c r="C64" s="52"/>
+      <c r="D64" s="52"/>
+      <c r="E64" s="52"/>
+      <c r="F64" s="52"/>
+    </row>
+    <row r="65" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A65" s="83" t="s">
+        <v>219</v>
+      </c>
+      <c r="B65" s="57" t="s">
+        <v>220</v>
+      </c>
+      <c r="C65" s="58" t="s">
+        <v>221</v>
+      </c>
+      <c r="D65" s="59" t="s">
+        <v>222</v>
+      </c>
+      <c r="E65" s="61"/>
+      <c r="F65" s="11" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="34.5" customHeight="1">
+      <c r="A66" s="83" t="s">
+        <v>219</v>
+      </c>
+      <c r="B66" s="57" t="s">
+        <v>225</v>
+      </c>
+      <c r="C66" s="58" t="s">
+        <v>226</v>
+      </c>
+      <c r="D66" s="59" t="s">
+        <v>227</v>
+      </c>
+      <c r="E66" s="61" t="s">
+        <v>415</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="14.25" customHeight="1">
+      <c r="E67" s="84"/>
+    </row>
+    <row r="68" spans="1:6" ht="14.25" customHeight="1">
+      <c r="E68" s="84"/>
+    </row>
+    <row r="69" spans="1:6" ht="14.25" customHeight="1">
+      <c r="E69" s="84"/>
+    </row>
+    <row r="70" spans="1:6" ht="14.25" customHeight="1">
+      <c r="E70" s="84"/>
+    </row>
+    <row r="71" spans="1:6" ht="14.25" customHeight="1">
+      <c r="E71" s="84"/>
+    </row>
+    <row r="72" spans="1:6" ht="14.25" customHeight="1">
+      <c r="E72" s="84"/>
+    </row>
+    <row r="73" spans="1:6" ht="14.25" customHeight="1">
+      <c r="E73" s="84"/>
+    </row>
+    <row r="74" spans="1:6" ht="14.25" customHeight="1">
+      <c r="E74" s="84"/>
+    </row>
+    <row r="75" spans="1:6" ht="14.25" customHeight="1">
+      <c r="E75" s="84"/>
+    </row>
+    <row r="76" spans="1:6" ht="14.25" customHeight="1">
+      <c r="E76" s="84"/>
+    </row>
+    <row r="77" spans="1:6" ht="14.25" customHeight="1">
+      <c r="E77" s="84"/>
+    </row>
+    <row r="78" spans="1:6" ht="14.25" customHeight="1">
+      <c r="E78" s="84"/>
+    </row>
+    <row r="79" spans="1:6" ht="14.25" customHeight="1">
+      <c r="E79" s="84"/>
+    </row>
+    <row r="80" spans="1:6" ht="14.25" customHeight="1">
+      <c r="E80" s="84"/>
+    </row>
+    <row r="81" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E81" s="84"/>
+    </row>
+    <row r="82" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E82" s="84"/>
+    </row>
+    <row r="83" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E83" s="84"/>
+    </row>
+    <row r="84" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E84" s="84"/>
+    </row>
+    <row r="85" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E85" s="84"/>
+    </row>
+    <row r="86" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E86" s="84"/>
+    </row>
+    <row r="87" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E87" s="84"/>
+    </row>
+    <row r="88" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E88" s="84"/>
+    </row>
+    <row r="89" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E89" s="84"/>
+    </row>
+    <row r="90" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E90" s="84"/>
+    </row>
+    <row r="91" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E91" s="84"/>
+    </row>
+    <row r="92" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E92" s="84"/>
+    </row>
+    <row r="93" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E93" s="84"/>
+    </row>
+    <row r="94" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E94" s="84"/>
+    </row>
+    <row r="95" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E95" s="84"/>
+    </row>
+    <row r="96" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E96" s="84"/>
+    </row>
+    <row r="97" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E97" s="84"/>
+    </row>
+    <row r="98" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E98" s="84"/>
+    </row>
+    <row r="99" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E99" s="84"/>
+    </row>
+    <row r="100" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E100" s="84"/>
+    </row>
+    <row r="101" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E101" s="84"/>
+    </row>
+    <row r="102" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E102" s="84"/>
+    </row>
+    <row r="103" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E103" s="84"/>
+    </row>
+    <row r="104" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E104" s="84"/>
+    </row>
+    <row r="105" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E105" s="84"/>
+    </row>
+    <row r="106" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E106" s="84"/>
+    </row>
+    <row r="107" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E107" s="84"/>
+    </row>
+    <row r="108" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E108" s="84"/>
+    </row>
+    <row r="109" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E109" s="84"/>
+    </row>
+    <row r="110" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E110" s="84"/>
+    </row>
+    <row r="111" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E111" s="84"/>
+    </row>
+    <row r="112" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E112" s="84"/>
+    </row>
+    <row r="113" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E113" s="84"/>
+    </row>
+    <row r="114" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E114" s="84"/>
+    </row>
+    <row r="115" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E115" s="84"/>
+    </row>
+    <row r="116" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E116" s="84"/>
+    </row>
+    <row r="117" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E117" s="84"/>
+    </row>
+    <row r="118" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E118" s="84"/>
+    </row>
+    <row r="119" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E119" s="84"/>
+    </row>
+    <row r="120" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E120" s="84"/>
+    </row>
+    <row r="121" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E121" s="84"/>
+    </row>
+    <row r="122" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E122" s="84"/>
+    </row>
+    <row r="123" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E123" s="84"/>
+    </row>
+    <row r="124" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E124" s="84"/>
+    </row>
+    <row r="125" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E125" s="84"/>
+    </row>
+    <row r="126" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E126" s="84"/>
+    </row>
+    <row r="127" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E127" s="84"/>
+    </row>
+    <row r="128" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E128" s="84"/>
+    </row>
+    <row r="129" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E129" s="84"/>
+    </row>
+    <row r="130" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E130" s="84"/>
+    </row>
+    <row r="131" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E131" s="84"/>
+    </row>
+    <row r="132" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E132" s="84"/>
+    </row>
+    <row r="133" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E133" s="84"/>
+    </row>
+    <row r="134" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E134" s="84"/>
+    </row>
+    <row r="135" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E135" s="84"/>
+    </row>
+    <row r="136" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E136" s="84"/>
+    </row>
+    <row r="137" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E137" s="84"/>
+    </row>
+    <row r="138" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E138" s="84"/>
+    </row>
+    <row r="139" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E139" s="84"/>
+    </row>
+    <row r="140" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E140" s="84"/>
+    </row>
+    <row r="141" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E141" s="84"/>
+    </row>
+    <row r="142" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E142" s="84"/>
+    </row>
+    <row r="143" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E143" s="84"/>
+    </row>
+    <row r="144" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E144" s="84"/>
+    </row>
+    <row r="145" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E145" s="84"/>
+    </row>
+    <row r="146" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E146" s="84"/>
+    </row>
+    <row r="147" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E147" s="84"/>
+    </row>
+    <row r="148" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E148" s="84"/>
+    </row>
+    <row r="149" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E149" s="84"/>
+    </row>
+    <row r="150" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E150" s="84"/>
+    </row>
+    <row r="151" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E151" s="84"/>
+    </row>
+    <row r="152" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E152" s="84"/>
+    </row>
+    <row r="153" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E153" s="84"/>
+    </row>
+    <row r="154" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E154" s="84"/>
+    </row>
+    <row r="155" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E155" s="84"/>
+    </row>
+    <row r="156" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E156" s="84"/>
+    </row>
+    <row r="157" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E157" s="84"/>
+    </row>
+    <row r="158" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E158" s="84"/>
+    </row>
+    <row r="159" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E159" s="84"/>
+    </row>
+    <row r="160" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E160" s="84"/>
+    </row>
+    <row r="161" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E161" s="84"/>
+    </row>
+    <row r="162" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E162" s="84"/>
+    </row>
+    <row r="163" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E163" s="84"/>
+    </row>
+    <row r="164" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E164" s="84"/>
+    </row>
+    <row r="165" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E165" s="84"/>
+    </row>
+    <row r="166" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E166" s="84"/>
+    </row>
+    <row r="167" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E167" s="84"/>
+    </row>
+    <row r="168" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E168" s="84"/>
+    </row>
+    <row r="169" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E169" s="84"/>
+    </row>
+    <row r="170" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E170" s="84"/>
+    </row>
+    <row r="171" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E171" s="84"/>
+    </row>
+    <row r="172" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E172" s="84"/>
+    </row>
+    <row r="173" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E173" s="84"/>
+    </row>
+    <row r="174" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E174" s="84"/>
+    </row>
+    <row r="175" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E175" s="84"/>
+    </row>
+    <row r="176" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E176" s="84"/>
+    </row>
+    <row r="177" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E177" s="84"/>
+    </row>
+    <row r="178" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E178" s="84"/>
+    </row>
+    <row r="179" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E179" s="84"/>
+    </row>
+    <row r="180" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E180" s="84"/>
+    </row>
+    <row r="181" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E181" s="84"/>
+    </row>
+    <row r="182" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E182" s="84"/>
+    </row>
+    <row r="183" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E183" s="84"/>
+    </row>
+    <row r="184" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E184" s="84"/>
+    </row>
+    <row r="185" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E185" s="84"/>
+    </row>
+    <row r="186" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E186" s="84"/>
+    </row>
+    <row r="187" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E187" s="84"/>
+    </row>
+    <row r="188" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E188" s="84"/>
+    </row>
+    <row r="189" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E189" s="84"/>
+    </row>
+    <row r="190" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E190" s="84"/>
+    </row>
+    <row r="191" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E191" s="84"/>
+    </row>
+    <row r="192" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E192" s="84"/>
+    </row>
+    <row r="193" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E193" s="84"/>
+    </row>
+    <row r="194" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E194" s="84"/>
+    </row>
+    <row r="195" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E195" s="84"/>
+    </row>
+    <row r="196" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E196" s="84"/>
+    </row>
+    <row r="197" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E197" s="84"/>
+    </row>
+    <row r="198" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E198" s="84"/>
+    </row>
+    <row r="199" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E199" s="84"/>
+    </row>
+    <row r="200" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E200" s="84"/>
+    </row>
+    <row r="201" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E201" s="84"/>
+    </row>
+    <row r="202" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E202" s="84"/>
+    </row>
+    <row r="203" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E203" s="84"/>
+    </row>
+    <row r="204" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E204" s="84"/>
+    </row>
+    <row r="205" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E205" s="84"/>
+    </row>
+    <row r="206" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E206" s="84"/>
+    </row>
+    <row r="207" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E207" s="84"/>
+    </row>
+    <row r="208" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E208" s="84"/>
+    </row>
+    <row r="209" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E209" s="84"/>
+    </row>
+    <row r="210" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E210" s="84"/>
+    </row>
+    <row r="211" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E211" s="84"/>
+    </row>
+    <row r="212" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E212" s="84"/>
+    </row>
+    <row r="213" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E213" s="84"/>
+    </row>
+    <row r="214" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E214" s="84"/>
+    </row>
+    <row r="215" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E215" s="84"/>
+    </row>
+    <row r="216" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E216" s="84"/>
+    </row>
+    <row r="217" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E217" s="84"/>
+    </row>
+    <row r="218" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E218" s="84"/>
+    </row>
+    <row r="219" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E219" s="84"/>
+    </row>
+    <row r="220" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E220" s="84"/>
+    </row>
+    <row r="221" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E221" s="84"/>
+    </row>
+    <row r="222" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E222" s="84"/>
+    </row>
+    <row r="223" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E223" s="84"/>
+    </row>
+    <row r="224" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E224" s="84"/>
+    </row>
+    <row r="225" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E225" s="84"/>
+    </row>
+    <row r="226" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E226" s="84"/>
+    </row>
+    <row r="227" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E227" s="84"/>
+    </row>
+    <row r="228" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E228" s="84"/>
+    </row>
+    <row r="229" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E229" s="84"/>
+    </row>
+    <row r="230" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E230" s="84"/>
+    </row>
+    <row r="231" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E231" s="84"/>
+    </row>
+    <row r="232" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E232" s="84"/>
+    </row>
+    <row r="233" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E233" s="84"/>
+    </row>
+    <row r="234" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E234" s="84"/>
+    </row>
+    <row r="235" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E235" s="84"/>
+    </row>
+    <row r="236" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E236" s="84"/>
+    </row>
+    <row r="237" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E237" s="84"/>
+    </row>
+    <row r="238" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E238" s="84"/>
+    </row>
+    <row r="239" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E239" s="84"/>
+    </row>
+    <row r="240" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E240" s="84"/>
+    </row>
+    <row r="241" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E241" s="84"/>
+    </row>
+    <row r="242" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E242" s="84"/>
+    </row>
+    <row r="243" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E243" s="84"/>
+    </row>
+    <row r="244" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E244" s="84"/>
+    </row>
+    <row r="245" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E245" s="84"/>
+    </row>
+    <row r="246" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E246" s="84"/>
+    </row>
+    <row r="247" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E247" s="84"/>
+    </row>
+    <row r="248" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E248" s="84"/>
+    </row>
+    <row r="249" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E249" s="84"/>
+    </row>
+    <row r="250" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E250" s="84"/>
+    </row>
+    <row r="251" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E251" s="84"/>
+    </row>
+    <row r="252" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E252" s="84"/>
+    </row>
+    <row r="253" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E253" s="84"/>
+    </row>
+    <row r="254" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E254" s="84"/>
+    </row>
+    <row r="255" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E255" s="84"/>
+    </row>
+    <row r="256" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E256" s="84"/>
+    </row>
+    <row r="257" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E257" s="84"/>
+    </row>
+    <row r="258" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E258" s="84"/>
+    </row>
+    <row r="259" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E259" s="84"/>
+    </row>
+    <row r="260" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E260" s="84"/>
+    </row>
+    <row r="261" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E261" s="84"/>
+    </row>
+    <row r="262" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E262" s="84"/>
+    </row>
+    <row r="263" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E263" s="84"/>
+    </row>
+    <row r="264" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E264" s="84"/>
+    </row>
+    <row r="265" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E265" s="84"/>
+    </row>
+    <row r="266" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E266" s="84"/>
+    </row>
+    <row r="267" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E267" s="84"/>
+    </row>
+    <row r="268" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E268" s="84"/>
+    </row>
+    <row r="269" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E269" s="84"/>
+    </row>
+    <row r="270" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E270" s="84"/>
+    </row>
+    <row r="271" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E271" s="84"/>
+    </row>
+    <row r="272" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E272" s="84"/>
+    </row>
+    <row r="273" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E273" s="84"/>
+    </row>
+    <row r="274" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E274" s="84"/>
+    </row>
+    <row r="275" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E275" s="84"/>
+    </row>
+    <row r="276" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E276" s="84"/>
+    </row>
+    <row r="277" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E277" s="84"/>
+    </row>
+    <row r="278" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E278" s="84"/>
+    </row>
+    <row r="279" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E279" s="84"/>
+    </row>
+    <row r="280" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E280" s="84"/>
+    </row>
+    <row r="281" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E281" s="84"/>
+    </row>
+    <row r="282" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E282" s="84"/>
+    </row>
+    <row r="283" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E283" s="84"/>
+    </row>
+    <row r="284" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E284" s="84"/>
+    </row>
+    <row r="285" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E285" s="84"/>
+    </row>
+    <row r="286" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E286" s="84"/>
+    </row>
+    <row r="287" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E287" s="84"/>
+    </row>
+    <row r="288" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E288" s="84"/>
+    </row>
+    <row r="289" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E289" s="84"/>
+    </row>
+    <row r="290" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E290" s="84"/>
+    </row>
+    <row r="291" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E291" s="84"/>
+    </row>
+    <row r="292" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E292" s="84"/>
+    </row>
+    <row r="293" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E293" s="84"/>
+    </row>
+    <row r="294" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E294" s="84"/>
+    </row>
+    <row r="295" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E295" s="84"/>
+    </row>
+    <row r="296" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E296" s="84"/>
+    </row>
+    <row r="297" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E297" s="84"/>
+    </row>
+    <row r="298" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E298" s="84"/>
+    </row>
+    <row r="299" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E299" s="84"/>
+    </row>
+    <row r="300" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E300" s="84"/>
+    </row>
+    <row r="301" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E301" s="84"/>
+    </row>
+    <row r="302" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E302" s="84"/>
+    </row>
+    <row r="303" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E303" s="84"/>
+    </row>
+    <row r="304" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E304" s="84"/>
+    </row>
+    <row r="305" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E305" s="84"/>
+    </row>
+    <row r="306" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E306" s="84"/>
+    </row>
+    <row r="307" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E307" s="84"/>
+    </row>
+    <row r="308" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E308" s="84"/>
+    </row>
+    <row r="309" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E309" s="84"/>
+    </row>
+    <row r="310" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E310" s="84"/>
+    </row>
+    <row r="311" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E311" s="84"/>
+    </row>
+    <row r="312" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E312" s="84"/>
+    </row>
+    <row r="313" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E313" s="84"/>
+    </row>
+    <row r="314" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E314" s="84"/>
+    </row>
+    <row r="315" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E315" s="84"/>
+    </row>
+    <row r="316" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E316" s="84"/>
+    </row>
+    <row r="317" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E317" s="84"/>
+    </row>
+    <row r="318" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E318" s="84"/>
+    </row>
+    <row r="319" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E319" s="84"/>
+    </row>
+    <row r="320" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E320" s="84"/>
+    </row>
+    <row r="321" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E321" s="84"/>
+    </row>
+    <row r="322" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E322" s="84"/>
+    </row>
+    <row r="323" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E323" s="84"/>
+    </row>
+    <row r="324" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E324" s="84"/>
+    </row>
+    <row r="325" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E325" s="84"/>
+    </row>
+    <row r="326" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E326" s="84"/>
+    </row>
+    <row r="327" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E327" s="84"/>
+    </row>
+    <row r="328" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E328" s="84"/>
+    </row>
+    <row r="329" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E329" s="84"/>
+    </row>
+    <row r="330" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E330" s="84"/>
+    </row>
+    <row r="331" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E331" s="84"/>
+    </row>
+    <row r="332" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E332" s="84"/>
+    </row>
+    <row r="333" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E333" s="84"/>
+    </row>
+    <row r="334" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E334" s="84"/>
+    </row>
+    <row r="335" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E335" s="84"/>
+    </row>
+    <row r="336" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E336" s="84"/>
+    </row>
+    <row r="337" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E337" s="84"/>
+    </row>
+    <row r="338" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E338" s="84"/>
+    </row>
+    <row r="339" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E339" s="84"/>
+    </row>
+    <row r="340" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E340" s="84"/>
+    </row>
+    <row r="341" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E341" s="84"/>
+    </row>
+    <row r="342" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E342" s="84"/>
+    </row>
+    <row r="343" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E343" s="84"/>
+    </row>
+    <row r="344" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E344" s="84"/>
+    </row>
+    <row r="345" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E345" s="84"/>
+    </row>
+    <row r="346" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E346" s="84"/>
+    </row>
+    <row r="347" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E347" s="84"/>
+    </row>
+    <row r="348" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E348" s="84"/>
+    </row>
+    <row r="349" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E349" s="84"/>
+    </row>
+    <row r="350" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E350" s="84"/>
+    </row>
+    <row r="351" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E351" s="84"/>
+    </row>
+    <row r="352" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E352" s="84"/>
+    </row>
+    <row r="353" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E353" s="84"/>
+    </row>
+    <row r="354" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E354" s="84"/>
+    </row>
+    <row r="355" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E355" s="84"/>
+    </row>
+    <row r="356" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E356" s="84"/>
+    </row>
+    <row r="357" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E357" s="84"/>
+    </row>
+    <row r="358" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E358" s="84"/>
+    </row>
+    <row r="359" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E359" s="84"/>
+    </row>
+    <row r="360" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E360" s="84"/>
+    </row>
+    <row r="361" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E361" s="84"/>
+    </row>
+    <row r="362" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E362" s="84"/>
+    </row>
+    <row r="363" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E363" s="84"/>
+    </row>
+    <row r="364" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E364" s="84"/>
+    </row>
+    <row r="365" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E365" s="84"/>
+    </row>
+    <row r="366" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E366" s="84"/>
+    </row>
+    <row r="367" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E367" s="84"/>
+    </row>
+    <row r="368" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E368" s="84"/>
+    </row>
+    <row r="369" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E369" s="84"/>
+    </row>
+    <row r="370" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E370" s="84"/>
+    </row>
+    <row r="371" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E371" s="84"/>
+    </row>
+    <row r="372" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E372" s="84"/>
+    </row>
+    <row r="373" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E373" s="84"/>
+    </row>
+    <row r="374" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E374" s="84"/>
+    </row>
+    <row r="375" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E375" s="84"/>
+    </row>
+    <row r="376" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E376" s="84"/>
+    </row>
+    <row r="377" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E377" s="84"/>
+    </row>
+    <row r="378" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E378" s="84"/>
+    </row>
+    <row r="379" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E379" s="84"/>
+    </row>
+    <row r="380" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E380" s="84"/>
+    </row>
+    <row r="381" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E381" s="84"/>
+    </row>
+    <row r="382" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E382" s="84"/>
+    </row>
+    <row r="383" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E383" s="84"/>
+    </row>
+    <row r="384" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E384" s="84"/>
+    </row>
+    <row r="385" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E385" s="84"/>
+    </row>
+    <row r="386" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E386" s="84"/>
+    </row>
+    <row r="387" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E387" s="84"/>
+    </row>
+    <row r="388" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E388" s="84"/>
+    </row>
+    <row r="389" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E389" s="84"/>
+    </row>
+    <row r="390" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E390" s="84"/>
+    </row>
+    <row r="391" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E391" s="84"/>
+    </row>
+    <row r="392" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E392" s="84"/>
+    </row>
+    <row r="393" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E393" s="84"/>
+    </row>
+    <row r="394" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E394" s="84"/>
+    </row>
+    <row r="395" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E395" s="84"/>
+    </row>
+    <row r="396" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E396" s="84"/>
+    </row>
+    <row r="397" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E397" s="84"/>
+    </row>
+    <row r="398" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E398" s="84"/>
+    </row>
+    <row r="399" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E399" s="84"/>
+    </row>
+    <row r="400" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E400" s="84"/>
+    </row>
+    <row r="401" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E401" s="84"/>
+    </row>
+    <row r="402" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E402" s="84"/>
+    </row>
+    <row r="403" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E403" s="84"/>
+    </row>
+    <row r="404" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E404" s="84"/>
+    </row>
+    <row r="405" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E405" s="84"/>
+    </row>
+    <row r="406" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E406" s="84"/>
+    </row>
+    <row r="407" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E407" s="84"/>
+    </row>
+    <row r="408" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E408" s="84"/>
+    </row>
+    <row r="409" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E409" s="84"/>
+    </row>
+    <row r="410" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E410" s="84"/>
+    </row>
+    <row r="411" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E411" s="84"/>
+    </row>
+    <row r="412" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E412" s="84"/>
+    </row>
+    <row r="413" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E413" s="84"/>
+    </row>
+    <row r="414" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E414" s="84"/>
+    </row>
+    <row r="415" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E415" s="84"/>
+    </row>
+    <row r="416" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E416" s="84"/>
+    </row>
+    <row r="417" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E417" s="84"/>
+    </row>
+    <row r="418" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E418" s="84"/>
+    </row>
+    <row r="419" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E419" s="84"/>
+    </row>
+    <row r="420" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E420" s="84"/>
+    </row>
+    <row r="421" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E421" s="84"/>
+    </row>
+    <row r="422" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E422" s="84"/>
+    </row>
+    <row r="423" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E423" s="84"/>
+    </row>
+    <row r="424" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E424" s="84"/>
+    </row>
+    <row r="425" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E425" s="84"/>
+    </row>
+    <row r="426" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E426" s="84"/>
+    </row>
+    <row r="427" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E427" s="84"/>
+    </row>
+    <row r="428" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E428" s="84"/>
+    </row>
+    <row r="429" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E429" s="84"/>
+    </row>
+    <row r="430" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E430" s="84"/>
+    </row>
+    <row r="431" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E431" s="84"/>
+    </row>
+    <row r="432" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E432" s="84"/>
+    </row>
+    <row r="433" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E433" s="84"/>
+    </row>
+    <row r="434" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E434" s="84"/>
+    </row>
+    <row r="435" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E435" s="84"/>
+    </row>
+    <row r="436" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E436" s="84"/>
+    </row>
+    <row r="437" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E437" s="84"/>
+    </row>
+    <row r="438" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E438" s="84"/>
+    </row>
+    <row r="439" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E439" s="84"/>
+    </row>
+    <row r="440" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E440" s="84"/>
+    </row>
+    <row r="441" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E441" s="84"/>
+    </row>
+    <row r="442" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E442" s="84"/>
+    </row>
+    <row r="443" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E443" s="84"/>
+    </row>
+    <row r="444" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E444" s="84"/>
+    </row>
+    <row r="445" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E445" s="84"/>
+    </row>
+    <row r="446" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E446" s="84"/>
+    </row>
+    <row r="447" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E447" s="84"/>
+    </row>
+    <row r="448" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E448" s="84"/>
+    </row>
+    <row r="449" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E449" s="84"/>
+    </row>
+    <row r="450" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E450" s="84"/>
+    </row>
+    <row r="451" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E451" s="84"/>
+    </row>
+    <row r="452" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E452" s="84"/>
+    </row>
+    <row r="453" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E453" s="84"/>
+    </row>
+    <row r="454" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E454" s="84"/>
+    </row>
+    <row r="455" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E455" s="84"/>
+    </row>
+    <row r="456" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E456" s="84"/>
+    </row>
+    <row r="457" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E457" s="84"/>
+    </row>
+    <row r="458" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E458" s="84"/>
+    </row>
+    <row r="459" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E459" s="84"/>
+    </row>
+    <row r="460" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E460" s="84"/>
+    </row>
+    <row r="461" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E461" s="84"/>
+    </row>
+    <row r="462" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E462" s="84"/>
+    </row>
+    <row r="463" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E463" s="84"/>
+    </row>
+    <row r="464" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E464" s="84"/>
+    </row>
+    <row r="465" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E465" s="84"/>
+    </row>
+    <row r="466" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E466" s="84"/>
+    </row>
+    <row r="467" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E467" s="84"/>
+    </row>
+    <row r="468" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E468" s="84"/>
+    </row>
+    <row r="469" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E469" s="84"/>
+    </row>
+    <row r="470" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E470" s="84"/>
+    </row>
+    <row r="471" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E471" s="84"/>
+    </row>
+    <row r="472" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E472" s="84"/>
+    </row>
+    <row r="473" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E473" s="84"/>
+    </row>
+    <row r="474" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E474" s="84"/>
+    </row>
+    <row r="475" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E475" s="84"/>
+    </row>
+    <row r="476" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E476" s="84"/>
+    </row>
+    <row r="477" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E477" s="84"/>
+    </row>
+    <row r="478" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E478" s="84"/>
+    </row>
+    <row r="479" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E479" s="84"/>
+    </row>
+    <row r="480" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E480" s="84"/>
+    </row>
+    <row r="481" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E481" s="84"/>
+    </row>
+    <row r="482" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E482" s="84"/>
+    </row>
+    <row r="483" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E483" s="84"/>
+    </row>
+    <row r="484" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E484" s="84"/>
+    </row>
+    <row r="485" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E485" s="84"/>
+    </row>
+    <row r="486" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E486" s="84"/>
+    </row>
+    <row r="487" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E487" s="84"/>
+    </row>
+    <row r="488" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E488" s="84"/>
+    </row>
+    <row r="489" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E489" s="84"/>
+    </row>
+    <row r="490" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E490" s="84"/>
+    </row>
+    <row r="491" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E491" s="84"/>
+    </row>
+    <row r="492" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E492" s="84"/>
+    </row>
+    <row r="493" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E493" s="84"/>
+    </row>
+    <row r="494" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E494" s="84"/>
+    </row>
+    <row r="495" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E495" s="84"/>
+    </row>
+    <row r="496" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E496" s="84"/>
+    </row>
+    <row r="497" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E497" s="84"/>
+    </row>
+    <row r="498" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E498" s="84"/>
+    </row>
+    <row r="499" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E499" s="84"/>
+    </row>
+    <row r="500" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E500" s="84"/>
+    </row>
+    <row r="501" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E501" s="84"/>
+    </row>
+    <row r="502" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E502" s="84"/>
+    </row>
+    <row r="503" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E503" s="84"/>
+    </row>
+    <row r="504" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E504" s="84"/>
+    </row>
+    <row r="505" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E505" s="84"/>
+    </row>
+    <row r="506" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E506" s="84"/>
+    </row>
+    <row r="507" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E507" s="84"/>
+    </row>
+    <row r="508" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E508" s="84"/>
+    </row>
+    <row r="509" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E509" s="84"/>
+    </row>
+    <row r="510" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E510" s="84"/>
+    </row>
+    <row r="511" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E511" s="84"/>
+    </row>
+    <row r="512" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E512" s="84"/>
+    </row>
+    <row r="513" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E513" s="84"/>
+    </row>
+    <row r="514" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E514" s="84"/>
+    </row>
+    <row r="515" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E515" s="84"/>
+    </row>
+    <row r="516" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E516" s="84"/>
+    </row>
+    <row r="517" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E517" s="84"/>
+    </row>
+    <row r="518" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E518" s="84"/>
+    </row>
+    <row r="519" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E519" s="84"/>
+    </row>
+    <row r="520" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E520" s="84"/>
+    </row>
+    <row r="521" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E521" s="84"/>
+    </row>
+    <row r="522" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E522" s="84"/>
+    </row>
+    <row r="523" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E523" s="84"/>
+    </row>
+    <row r="524" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E524" s="84"/>
+    </row>
+    <row r="525" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E525" s="84"/>
+    </row>
+    <row r="526" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E526" s="84"/>
+    </row>
+    <row r="527" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E527" s="84"/>
+    </row>
+    <row r="528" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E528" s="84"/>
+    </row>
+    <row r="529" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E529" s="84"/>
+    </row>
+    <row r="530" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E530" s="84"/>
+    </row>
+    <row r="531" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E531" s="84"/>
+    </row>
+    <row r="532" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E532" s="84"/>
+    </row>
+    <row r="533" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E533" s="84"/>
+    </row>
+    <row r="534" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E534" s="84"/>
+    </row>
+    <row r="535" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E535" s="84"/>
+    </row>
+    <row r="536" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E536" s="84"/>
+    </row>
+    <row r="537" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E537" s="84"/>
+    </row>
+    <row r="538" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E538" s="84"/>
+    </row>
+    <row r="539" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E539" s="84"/>
+    </row>
+    <row r="540" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E540" s="84"/>
+    </row>
+    <row r="541" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E541" s="84"/>
+    </row>
+    <row r="542" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E542" s="84"/>
+    </row>
+    <row r="543" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E543" s="84"/>
+    </row>
+    <row r="544" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E544" s="84"/>
+    </row>
+    <row r="545" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E545" s="84"/>
+    </row>
+    <row r="546" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E546" s="84"/>
+    </row>
+    <row r="547" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E547" s="84"/>
+    </row>
+    <row r="548" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E548" s="84"/>
+    </row>
+    <row r="549" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E549" s="84"/>
+    </row>
+    <row r="550" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E550" s="84"/>
+    </row>
+    <row r="551" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E551" s="84"/>
+    </row>
+    <row r="552" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E552" s="84"/>
+    </row>
+    <row r="553" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E553" s="84"/>
+    </row>
+    <row r="554" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E554" s="84"/>
+    </row>
+    <row r="555" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E555" s="84"/>
+    </row>
+    <row r="556" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E556" s="84"/>
+    </row>
+    <row r="557" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E557" s="84"/>
+    </row>
+    <row r="558" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E558" s="84"/>
+    </row>
+    <row r="559" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E559" s="84"/>
+    </row>
+    <row r="560" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E560" s="84"/>
+    </row>
+    <row r="561" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E561" s="84"/>
+    </row>
+    <row r="562" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E562" s="84"/>
+    </row>
+    <row r="563" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E563" s="84"/>
+    </row>
+    <row r="564" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E564" s="84"/>
+    </row>
+    <row r="565" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E565" s="84"/>
+    </row>
+    <row r="566" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E566" s="84"/>
+    </row>
+    <row r="567" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E567" s="84"/>
+    </row>
+    <row r="568" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E568" s="84"/>
+    </row>
+    <row r="569" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E569" s="84"/>
+    </row>
+    <row r="570" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E570" s="84"/>
+    </row>
+    <row r="571" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E571" s="84"/>
+    </row>
+    <row r="572" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E572" s="84"/>
+    </row>
+    <row r="573" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E573" s="84"/>
+    </row>
+    <row r="574" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E574" s="84"/>
+    </row>
+    <row r="575" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E575" s="84"/>
+    </row>
+    <row r="576" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E576" s="84"/>
+    </row>
+    <row r="577" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E577" s="84"/>
+    </row>
+    <row r="578" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E578" s="84"/>
+    </row>
+    <row r="579" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E579" s="84"/>
+    </row>
+    <row r="580" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E580" s="84"/>
+    </row>
+    <row r="581" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E581" s="84"/>
+    </row>
+    <row r="582" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E582" s="84"/>
+    </row>
+    <row r="583" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E583" s="84"/>
+    </row>
+    <row r="584" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E584" s="84"/>
+    </row>
+    <row r="585" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E585" s="84"/>
+    </row>
+    <row r="586" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E586" s="84"/>
+    </row>
+    <row r="587" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E587" s="84"/>
+    </row>
+    <row r="588" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E588" s="84"/>
+    </row>
+    <row r="589" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E589" s="84"/>
+    </row>
+    <row r="590" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E590" s="84"/>
+    </row>
+    <row r="591" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E591" s="84"/>
+    </row>
+    <row r="592" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E592" s="84"/>
+    </row>
+    <row r="593" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E593" s="84"/>
+    </row>
+    <row r="594" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E594" s="84"/>
+    </row>
+    <row r="595" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E595" s="84"/>
+    </row>
+    <row r="596" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E596" s="84"/>
+    </row>
+    <row r="597" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E597" s="84"/>
+    </row>
+    <row r="598" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E598" s="84"/>
+    </row>
+    <row r="599" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E599" s="84"/>
+    </row>
+    <row r="600" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E600" s="84"/>
+    </row>
+    <row r="601" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E601" s="84"/>
+    </row>
+    <row r="602" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E602" s="84"/>
+    </row>
+    <row r="603" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E603" s="84"/>
+    </row>
+    <row r="604" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E604" s="84"/>
+    </row>
+    <row r="605" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E605" s="84"/>
+    </row>
+    <row r="606" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E606" s="84"/>
+    </row>
+    <row r="607" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E607" s="84"/>
+    </row>
+    <row r="608" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E608" s="84"/>
+    </row>
+    <row r="609" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E609" s="84"/>
+    </row>
+    <row r="610" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E610" s="84"/>
+    </row>
+    <row r="611" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E611" s="84"/>
+    </row>
+    <row r="612" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E612" s="84"/>
+    </row>
+    <row r="613" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E613" s="84"/>
+    </row>
+    <row r="614" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E614" s="84"/>
+    </row>
+    <row r="615" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E615" s="84"/>
+    </row>
+    <row r="616" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E616" s="84"/>
+    </row>
+    <row r="617" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E617" s="84"/>
+    </row>
+    <row r="618" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E618" s="84"/>
+    </row>
+    <row r="619" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E619" s="84"/>
+    </row>
+    <row r="620" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E620" s="84"/>
+    </row>
+    <row r="621" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E621" s="84"/>
+    </row>
+    <row r="622" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E622" s="84"/>
+    </row>
+    <row r="623" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E623" s="84"/>
+    </row>
+    <row r="624" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E624" s="84"/>
+    </row>
+    <row r="625" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E625" s="84"/>
+    </row>
+    <row r="626" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E626" s="84"/>
+    </row>
+    <row r="627" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E627" s="84"/>
+    </row>
+    <row r="628" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E628" s="84"/>
+    </row>
+    <row r="629" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E629" s="84"/>
+    </row>
+    <row r="630" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E630" s="84"/>
+    </row>
+    <row r="631" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E631" s="84"/>
+    </row>
+    <row r="632" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E632" s="84"/>
+    </row>
+    <row r="633" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E633" s="84"/>
+    </row>
+    <row r="634" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E634" s="84"/>
+    </row>
+    <row r="635" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E635" s="84"/>
+    </row>
+    <row r="636" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E636" s="84"/>
+    </row>
+    <row r="637" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E637" s="84"/>
+    </row>
+    <row r="638" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E638" s="84"/>
+    </row>
+    <row r="639" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E639" s="84"/>
+    </row>
+    <row r="640" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E640" s="84"/>
+    </row>
+    <row r="641" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E641" s="84"/>
+    </row>
+    <row r="642" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E642" s="84"/>
+    </row>
+    <row r="643" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E643" s="84"/>
+    </row>
+    <row r="644" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E644" s="84"/>
+    </row>
+    <row r="645" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E645" s="84"/>
+    </row>
+    <row r="646" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E646" s="84"/>
+    </row>
+    <row r="647" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E647" s="84"/>
+    </row>
+    <row r="648" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E648" s="84"/>
+    </row>
+    <row r="649" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E649" s="84"/>
+    </row>
+    <row r="650" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E650" s="84"/>
+    </row>
+    <row r="651" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E651" s="84"/>
+    </row>
+    <row r="652" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E652" s="84"/>
+    </row>
+    <row r="653" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E653" s="84"/>
+    </row>
+    <row r="654" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E654" s="84"/>
+    </row>
+    <row r="655" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E655" s="84"/>
+    </row>
+    <row r="656" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E656" s="84"/>
+    </row>
+    <row r="657" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E657" s="84"/>
+    </row>
+    <row r="658" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E658" s="84"/>
+    </row>
+    <row r="659" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E659" s="84"/>
+    </row>
+    <row r="660" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E660" s="84"/>
+    </row>
+    <row r="661" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E661" s="84"/>
+    </row>
+    <row r="662" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E662" s="84"/>
+    </row>
+    <row r="663" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E663" s="84"/>
+    </row>
+    <row r="664" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E664" s="84"/>
+    </row>
+    <row r="665" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E665" s="84"/>
+    </row>
+    <row r="666" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E666" s="84"/>
+    </row>
+    <row r="667" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E667" s="84"/>
+    </row>
+    <row r="668" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E668" s="84"/>
+    </row>
+    <row r="669" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E669" s="84"/>
+    </row>
+    <row r="670" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E670" s="84"/>
+    </row>
+    <row r="671" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E671" s="84"/>
+    </row>
+    <row r="672" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E672" s="84"/>
+    </row>
+    <row r="673" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E673" s="84"/>
+    </row>
+    <row r="674" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E674" s="84"/>
+    </row>
+    <row r="675" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E675" s="84"/>
+    </row>
+    <row r="676" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E676" s="84"/>
+    </row>
+    <row r="677" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E677" s="84"/>
+    </row>
+    <row r="678" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E678" s="84"/>
+    </row>
+    <row r="679" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E679" s="84"/>
+    </row>
+    <row r="680" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E680" s="84"/>
+    </row>
+    <row r="681" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E681" s="84"/>
+    </row>
+    <row r="682" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E682" s="84"/>
+    </row>
+    <row r="683" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E683" s="84"/>
+    </row>
+    <row r="684" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E684" s="84"/>
+    </row>
+    <row r="685" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E685" s="84"/>
+    </row>
+    <row r="686" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E686" s="84"/>
+    </row>
+    <row r="687" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E687" s="84"/>
+    </row>
+    <row r="688" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E688" s="84"/>
+    </row>
+    <row r="689" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E689" s="84"/>
+    </row>
+    <row r="690" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E690" s="84"/>
+    </row>
+    <row r="691" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E691" s="84"/>
+    </row>
+    <row r="692" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E692" s="84"/>
+    </row>
+    <row r="693" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E693" s="84"/>
+    </row>
+    <row r="694" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E694" s="84"/>
+    </row>
+    <row r="695" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E695" s="84"/>
+    </row>
+    <row r="696" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E696" s="84"/>
+    </row>
+    <row r="697" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E697" s="84"/>
+    </row>
+    <row r="698" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E698" s="84"/>
+    </row>
+    <row r="699" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E699" s="84"/>
+    </row>
+    <row r="700" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E700" s="84"/>
+    </row>
+    <row r="701" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E701" s="84"/>
+    </row>
+    <row r="702" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E702" s="84"/>
+    </row>
+    <row r="703" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E703" s="84"/>
+    </row>
+    <row r="704" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E704" s="84"/>
+    </row>
+    <row r="705" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E705" s="84"/>
+    </row>
+    <row r="706" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E706" s="84"/>
+    </row>
+    <row r="707" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E707" s="84"/>
+    </row>
+    <row r="708" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E708" s="84"/>
+    </row>
+    <row r="709" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E709" s="84"/>
+    </row>
+    <row r="710" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E710" s="84"/>
+    </row>
+    <row r="711" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E711" s="84"/>
+    </row>
+    <row r="712" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E712" s="84"/>
+    </row>
+    <row r="713" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E713" s="84"/>
+    </row>
+    <row r="714" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E714" s="84"/>
+    </row>
+    <row r="715" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E715" s="84"/>
+    </row>
+    <row r="716" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E716" s="84"/>
+    </row>
+    <row r="717" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E717" s="84"/>
+    </row>
+    <row r="718" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E718" s="84"/>
+    </row>
+    <row r="719" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E719" s="84"/>
+    </row>
+    <row r="720" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E720" s="84"/>
+    </row>
+    <row r="721" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E721" s="84"/>
+    </row>
+    <row r="722" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E722" s="84"/>
+    </row>
+    <row r="723" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E723" s="84"/>
+    </row>
+    <row r="724" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E724" s="84"/>
+    </row>
+    <row r="725" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E725" s="84"/>
+    </row>
+    <row r="726" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E726" s="84"/>
+    </row>
+    <row r="727" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E727" s="84"/>
+    </row>
+    <row r="728" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E728" s="84"/>
+    </row>
+    <row r="729" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E729" s="84"/>
+    </row>
+    <row r="730" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E730" s="84"/>
+    </row>
+    <row r="731" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E731" s="84"/>
+    </row>
+    <row r="732" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E732" s="84"/>
+    </row>
+    <row r="733" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E733" s="84"/>
+    </row>
+    <row r="734" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E734" s="84"/>
+    </row>
+    <row r="735" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E735" s="84"/>
+    </row>
+    <row r="736" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E736" s="84"/>
+    </row>
+    <row r="737" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E737" s="84"/>
+    </row>
+    <row r="738" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E738" s="84"/>
+    </row>
+    <row r="739" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E739" s="84"/>
+    </row>
+    <row r="740" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E740" s="84"/>
+    </row>
+    <row r="741" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E741" s="84"/>
+    </row>
+    <row r="742" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E742" s="84"/>
+    </row>
+    <row r="743" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E743" s="84"/>
+    </row>
+    <row r="744" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E744" s="84"/>
+    </row>
+    <row r="745" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E745" s="84"/>
+    </row>
+    <row r="746" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E746" s="84"/>
+    </row>
+    <row r="747" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E747" s="84"/>
+    </row>
+    <row r="748" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E748" s="84"/>
+    </row>
+    <row r="749" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E749" s="84"/>
+    </row>
+    <row r="750" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E750" s="84"/>
+    </row>
+    <row r="751" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E751" s="84"/>
+    </row>
+    <row r="752" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E752" s="84"/>
+    </row>
+    <row r="753" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E753" s="84"/>
+    </row>
+    <row r="754" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E754" s="84"/>
+    </row>
+    <row r="755" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E755" s="84"/>
+    </row>
+    <row r="756" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E756" s="84"/>
+    </row>
+    <row r="757" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E757" s="84"/>
+    </row>
+    <row r="758" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E758" s="84"/>
+    </row>
+    <row r="759" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E759" s="84"/>
+    </row>
+    <row r="760" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E760" s="84"/>
+    </row>
+    <row r="761" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E761" s="84"/>
+    </row>
+    <row r="762" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E762" s="84"/>
+    </row>
+    <row r="763" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E763" s="84"/>
+    </row>
+    <row r="764" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E764" s="84"/>
+    </row>
+    <row r="765" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E765" s="84"/>
+    </row>
+    <row r="766" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E766" s="84"/>
+    </row>
+    <row r="767" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E767" s="84"/>
+    </row>
+    <row r="768" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E768" s="84"/>
+    </row>
+    <row r="769" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E769" s="84"/>
+    </row>
+    <row r="770" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E770" s="84"/>
+    </row>
+    <row r="771" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E771" s="84"/>
+    </row>
+    <row r="772" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E772" s="84"/>
+    </row>
+    <row r="773" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E773" s="84"/>
+    </row>
+    <row r="774" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E774" s="84"/>
+    </row>
+    <row r="775" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E775" s="84"/>
+    </row>
+    <row r="776" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E776" s="84"/>
+    </row>
+    <row r="777" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E777" s="84"/>
+    </row>
+    <row r="778" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E778" s="84"/>
+    </row>
+    <row r="779" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E779" s="84"/>
+    </row>
+    <row r="780" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E780" s="84"/>
+    </row>
+    <row r="781" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E781" s="84"/>
+    </row>
+    <row r="782" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E782" s="84"/>
+    </row>
+    <row r="783" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E783" s="84"/>
+    </row>
+    <row r="784" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E784" s="84"/>
+    </row>
+    <row r="785" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E785" s="84"/>
+    </row>
+    <row r="786" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E786" s="84"/>
+    </row>
+    <row r="787" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E787" s="84"/>
+    </row>
+    <row r="788" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E788" s="84"/>
+    </row>
+    <row r="789" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E789" s="84"/>
+    </row>
+    <row r="790" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E790" s="84"/>
+    </row>
+    <row r="791" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E791" s="84"/>
+    </row>
+    <row r="792" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E792" s="84"/>
+    </row>
+    <row r="793" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E793" s="84"/>
+    </row>
+    <row r="794" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E794" s="84"/>
+    </row>
+    <row r="795" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E795" s="84"/>
+    </row>
+    <row r="796" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E796" s="84"/>
+    </row>
+    <row r="797" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E797" s="84"/>
+    </row>
+    <row r="798" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E798" s="84"/>
+    </row>
+    <row r="799" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E799" s="84"/>
+    </row>
+    <row r="800" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E800" s="84"/>
+    </row>
+    <row r="801" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E801" s="84"/>
+    </row>
+    <row r="802" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E802" s="84"/>
+    </row>
+    <row r="803" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E803" s="84"/>
+    </row>
+    <row r="804" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E804" s="84"/>
+    </row>
+    <row r="805" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E805" s="84"/>
+    </row>
+    <row r="806" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E806" s="84"/>
+    </row>
+    <row r="807" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E807" s="84"/>
+    </row>
+    <row r="808" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E808" s="84"/>
+    </row>
+    <row r="809" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E809" s="84"/>
+    </row>
+    <row r="810" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E810" s="84"/>
+    </row>
+    <row r="811" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E811" s="84"/>
+    </row>
+    <row r="812" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E812" s="84"/>
+    </row>
+    <row r="813" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E813" s="84"/>
+    </row>
+    <row r="814" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E814" s="84"/>
+    </row>
+    <row r="815" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E815" s="84"/>
+    </row>
+    <row r="816" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E816" s="84"/>
+    </row>
+    <row r="817" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E817" s="84"/>
+    </row>
+    <row r="818" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E818" s="84"/>
+    </row>
+    <row r="819" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E819" s="84"/>
+    </row>
+    <row r="820" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E820" s="84"/>
+    </row>
+    <row r="821" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E821" s="84"/>
+    </row>
+    <row r="822" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E822" s="84"/>
+    </row>
+    <row r="823" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E823" s="84"/>
+    </row>
+    <row r="824" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E824" s="84"/>
+    </row>
+    <row r="825" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E825" s="84"/>
+    </row>
+    <row r="826" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E826" s="84"/>
+    </row>
+    <row r="827" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E827" s="84"/>
+    </row>
+    <row r="828" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E828" s="84"/>
+    </row>
+    <row r="829" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E829" s="84"/>
+    </row>
+    <row r="830" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E830" s="84"/>
+    </row>
+    <row r="831" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E831" s="84"/>
+    </row>
+    <row r="832" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E832" s="84"/>
+    </row>
+    <row r="833" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E833" s="84"/>
+    </row>
+    <row r="834" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E834" s="84"/>
+    </row>
+    <row r="835" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E835" s="84"/>
+    </row>
+    <row r="836" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E836" s="84"/>
+    </row>
+    <row r="837" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E837" s="84"/>
+    </row>
+    <row r="838" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E838" s="84"/>
+    </row>
+    <row r="839" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E839" s="84"/>
+    </row>
+    <row r="840" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E840" s="84"/>
+    </row>
+    <row r="841" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E841" s="84"/>
+    </row>
+    <row r="842" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E842" s="84"/>
+    </row>
+    <row r="843" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E843" s="84"/>
+    </row>
+    <row r="844" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E844" s="84"/>
+    </row>
+    <row r="845" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E845" s="84"/>
+    </row>
+    <row r="846" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E846" s="84"/>
+    </row>
+    <row r="847" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E847" s="84"/>
+    </row>
+    <row r="848" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E848" s="84"/>
+    </row>
+    <row r="849" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E849" s="84"/>
+    </row>
+    <row r="850" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E850" s="84"/>
+    </row>
+    <row r="851" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E851" s="84"/>
+    </row>
+    <row r="852" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E852" s="84"/>
+    </row>
+    <row r="853" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E853" s="84"/>
+    </row>
+    <row r="854" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E854" s="84"/>
+    </row>
+    <row r="855" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E855" s="84"/>
+    </row>
+    <row r="856" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E856" s="84"/>
+    </row>
+    <row r="857" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E857" s="84"/>
+    </row>
+    <row r="858" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E858" s="84"/>
+    </row>
+    <row r="859" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E859" s="84"/>
+    </row>
+    <row r="860" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E860" s="84"/>
+    </row>
+    <row r="861" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E861" s="84"/>
+    </row>
+    <row r="862" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E862" s="84"/>
+    </row>
+    <row r="863" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E863" s="84"/>
+    </row>
+    <row r="864" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E864" s="84"/>
+    </row>
+    <row r="865" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E865" s="84"/>
+    </row>
+    <row r="866" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E866" s="84"/>
+    </row>
+    <row r="867" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E867" s="84"/>
+    </row>
+    <row r="868" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E868" s="84"/>
+    </row>
+    <row r="869" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E869" s="84"/>
+    </row>
+    <row r="870" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E870" s="84"/>
+    </row>
+    <row r="871" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E871" s="84"/>
+    </row>
+    <row r="872" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E872" s="84"/>
+    </row>
+    <row r="873" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E873" s="84"/>
+    </row>
+    <row r="874" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E874" s="84"/>
+    </row>
+    <row r="875" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E875" s="84"/>
+    </row>
+    <row r="876" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E876" s="84"/>
+    </row>
+    <row r="877" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E877" s="84"/>
+    </row>
+    <row r="878" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E878" s="84"/>
+    </row>
+    <row r="879" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E879" s="84"/>
+    </row>
+    <row r="880" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E880" s="84"/>
+    </row>
+    <row r="881" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E881" s="84"/>
+    </row>
+    <row r="882" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E882" s="84"/>
+    </row>
+    <row r="883" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E883" s="84"/>
+    </row>
+    <row r="884" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E884" s="84"/>
+    </row>
+    <row r="885" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E885" s="84"/>
+    </row>
+    <row r="886" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E886" s="84"/>
+    </row>
+    <row r="887" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E887" s="84"/>
+    </row>
+    <row r="888" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E888" s="84"/>
+    </row>
+    <row r="889" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E889" s="84"/>
+    </row>
+    <row r="890" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E890" s="84"/>
+    </row>
+    <row r="891" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E891" s="84"/>
+    </row>
+    <row r="892" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E892" s="84"/>
+    </row>
+    <row r="893" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E893" s="84"/>
+    </row>
+    <row r="894" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E894" s="84"/>
+    </row>
+    <row r="895" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E895" s="84"/>
+    </row>
+    <row r="896" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E896" s="84"/>
+    </row>
+    <row r="897" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E897" s="84"/>
+    </row>
+    <row r="898" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E898" s="84"/>
+    </row>
+    <row r="899" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E899" s="84"/>
+    </row>
+    <row r="900" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E900" s="84"/>
+    </row>
+    <row r="901" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E901" s="84"/>
+    </row>
+    <row r="902" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E902" s="84"/>
+    </row>
+    <row r="903" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E903" s="84"/>
+    </row>
+    <row r="904" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E904" s="84"/>
+    </row>
+    <row r="905" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E905" s="84"/>
+    </row>
+    <row r="906" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E906" s="84"/>
+    </row>
+    <row r="907" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E907" s="84"/>
+    </row>
+    <row r="908" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E908" s="84"/>
+    </row>
+    <row r="909" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E909" s="84"/>
+    </row>
+    <row r="910" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E910" s="84"/>
+    </row>
+    <row r="911" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E911" s="84"/>
+    </row>
+    <row r="912" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E912" s="84"/>
+    </row>
+    <row r="913" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E913" s="84"/>
+    </row>
+    <row r="914" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E914" s="84"/>
+    </row>
+    <row r="915" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E915" s="84"/>
+    </row>
+    <row r="916" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E916" s="84"/>
+    </row>
+    <row r="917" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E917" s="84"/>
+    </row>
+    <row r="918" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E918" s="84"/>
+    </row>
+    <row r="919" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E919" s="84"/>
+    </row>
+    <row r="920" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E920" s="84"/>
+    </row>
+    <row r="921" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E921" s="84"/>
+    </row>
+    <row r="922" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E922" s="84"/>
+    </row>
+    <row r="923" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E923" s="84"/>
+    </row>
+    <row r="924" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E924" s="84"/>
+    </row>
+    <row r="925" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E925" s="84"/>
+    </row>
+    <row r="926" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E926" s="84"/>
+    </row>
+    <row r="927" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E927" s="84"/>
+    </row>
+    <row r="928" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E928" s="84"/>
+    </row>
+    <row r="929" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E929" s="84"/>
+    </row>
+    <row r="930" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E930" s="84"/>
+    </row>
+    <row r="931" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E931" s="84"/>
+    </row>
+    <row r="932" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E932" s="84"/>
+    </row>
+    <row r="933" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E933" s="84"/>
+    </row>
+    <row r="934" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E934" s="84"/>
+    </row>
+    <row r="935" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E935" s="84"/>
+    </row>
+    <row r="936" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E936" s="84"/>
+    </row>
+    <row r="937" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E937" s="84"/>
+    </row>
+    <row r="938" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E938" s="84"/>
+    </row>
+    <row r="939" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E939" s="84"/>
+    </row>
+    <row r="940" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E940" s="84"/>
+    </row>
+    <row r="941" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E941" s="84"/>
+    </row>
+    <row r="942" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E942" s="84"/>
+    </row>
+    <row r="943" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E943" s="84"/>
+    </row>
+    <row r="944" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E944" s="84"/>
+    </row>
+    <row r="945" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E945" s="84"/>
+    </row>
+    <row r="946" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E946" s="84"/>
+    </row>
+    <row r="947" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E947" s="84"/>
+    </row>
+    <row r="948" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E948" s="84"/>
+    </row>
+    <row r="949" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E949" s="84"/>
+    </row>
+    <row r="950" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E950" s="84"/>
+    </row>
+    <row r="951" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E951" s="84"/>
+    </row>
+    <row r="952" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E952" s="84"/>
+    </row>
+    <row r="953" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E953" s="84"/>
+    </row>
+    <row r="954" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E954" s="84"/>
+    </row>
+    <row r="955" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E955" s="84"/>
+    </row>
+    <row r="956" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E956" s="84"/>
+    </row>
+    <row r="957" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E957" s="84"/>
+    </row>
+    <row r="958" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E958" s="84"/>
+    </row>
+    <row r="959" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E959" s="84"/>
+    </row>
+    <row r="960" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E960" s="84"/>
+    </row>
+    <row r="961" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E961" s="84"/>
+    </row>
+    <row r="962" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E962" s="84"/>
+    </row>
+    <row r="963" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E963" s="84"/>
+    </row>
+    <row r="964" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E964" s="84"/>
+    </row>
+    <row r="965" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E965" s="84"/>
+    </row>
+    <row r="966" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E966" s="84"/>
+    </row>
+    <row r="967" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E967" s="84"/>
+    </row>
+    <row r="968" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E968" s="84"/>
+    </row>
+    <row r="969" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E969" s="84"/>
+    </row>
+    <row r="970" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E970" s="84"/>
+    </row>
+    <row r="971" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E971" s="84"/>
+    </row>
+    <row r="972" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E972" s="84"/>
+    </row>
+    <row r="973" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E973" s="84"/>
+    </row>
+    <row r="974" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E974" s="84"/>
+    </row>
+    <row r="975" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E975" s="84"/>
+    </row>
+    <row r="976" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E976" s="84"/>
+    </row>
+    <row r="977" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E977" s="84"/>
+    </row>
+    <row r="978" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E978" s="84"/>
+    </row>
+    <row r="979" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E979" s="84"/>
+    </row>
+    <row r="980" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E980" s="84"/>
+    </row>
+    <row r="981" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E981" s="84"/>
+    </row>
+    <row r="982" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E982" s="84"/>
+    </row>
+    <row r="983" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E983" s="84"/>
+    </row>
+    <row r="984" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E984" s="84"/>
+    </row>
+    <row r="985" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E985" s="84"/>
+    </row>
+    <row r="986" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E986" s="84"/>
+    </row>
+    <row r="987" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E987" s="84"/>
+    </row>
+    <row r="988" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E988" s="84"/>
+    </row>
+    <row r="989" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E989" s="84"/>
+    </row>
+    <row r="990" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E990" s="84"/>
+    </row>
+    <row r="991" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E991" s="84"/>
+    </row>
+    <row r="992" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E992" s="84"/>
+    </row>
+    <row r="993" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E993" s="84"/>
+    </row>
+    <row r="994" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E994" s="84"/>
+    </row>
+    <row r="995" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E995" s="84"/>
+    </row>
+    <row r="996" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E996" s="84"/>
+    </row>
+    <row r="997" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E997" s="84"/>
+    </row>
+    <row r="998" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E998" s="84"/>
+    </row>
+    <row r="999" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E999" s="84"/>
+    </row>
+    <row r="1000" spans="5:5" ht="14.25" customHeight="1">
+      <c r="E1000" s="84"/>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A23:F23"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F66"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -5583,8 +9932,8 @@
     <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:6" ht="35" customHeight="1">
+      <c r="A1" s="34" t="s">
         <v>252</v>
       </c>
       <c r="B1" s="28"/>
@@ -5593,7 +9942,7 @@
       <c r="E1" s="28"/>
       <c r="F1" s="28"/>
     </row>
-    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="30" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
@@ -5613,8 +9962,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
+    <row r="3" spans="1:6" ht="25" customHeight="1">
+      <c r="A3" s="41" t="s">
         <v>34</v>
       </c>
       <c r="B3" s="28"/>
@@ -5623,8 +9972,8 @@
       <c r="E3" s="28"/>
       <c r="F3" s="28"/>
     </row>
-    <row r="4" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="33" t="s">
+    <row r="4" spans="1:6" ht="20" customHeight="1">
+      <c r="A4" s="39" t="s">
         <v>35</v>
       </c>
       <c r="B4" s="28"/>
@@ -5633,7 +9982,7 @@
       <c r="E4" s="28"/>
       <c r="F4" s="28"/>
     </row>
-    <row r="5" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="35" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>36</v>
       </c>
@@ -5651,7 +10000,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="40" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>36</v>
       </c>
@@ -5669,7 +10018,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="42" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>36</v>
       </c>
@@ -5687,7 +10036,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="38" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>36</v>
       </c>
@@ -5705,7 +10054,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="35" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>36</v>
       </c>
@@ -5723,7 +10072,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="35" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>36</v>
       </c>
@@ -5741,7 +10090,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="35" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>36</v>
       </c>
@@ -5759,7 +10108,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="36" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>36</v>
       </c>
@@ -5777,7 +10126,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="37.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="37" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
@@ -5795,7 +10144,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="35" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>36</v>
       </c>
@@ -5813,7 +10162,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="36" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>36</v>
       </c>
@@ -5831,7 +10180,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="35" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>36</v>
       </c>
@@ -5849,8 +10198,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="31" t="s">
+    <row r="17" spans="1:6" ht="25" customHeight="1">
+      <c r="A17" s="37" t="s">
         <v>86</v>
       </c>
       <c r="B17" s="28"/>
@@ -5859,8 +10208,8 @@
       <c r="E17" s="28"/>
       <c r="F17" s="28"/>
     </row>
-    <row r="18" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="32" t="s">
+    <row r="18" spans="1:6" ht="20" customHeight="1">
+      <c r="A18" s="38" t="s">
         <v>87</v>
       </c>
       <c r="B18" s="28"/>
@@ -5869,7 +10218,7 @@
       <c r="E18" s="28"/>
       <c r="F18" s="28"/>
     </row>
-    <row r="19" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="35" customHeight="1">
       <c r="A19" s="8" t="s">
         <v>88</v>
       </c>
@@ -5887,7 +10236,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="37.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="37" customHeight="1">
       <c r="A20" s="8" t="s">
         <v>88</v>
       </c>
@@ -5905,7 +10254,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="36" customHeight="1">
       <c r="A21" s="8" t="s">
         <v>88</v>
       </c>
@@ -5923,7 +10272,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="36" customHeight="1">
       <c r="A22" s="8" t="s">
         <v>88</v>
       </c>
@@ -5941,8 +10290,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="29" t="s">
+    <row r="23" spans="1:6" ht="25" customHeight="1">
+      <c r="A23" s="35" t="s">
         <v>104</v>
       </c>
       <c r="B23" s="28"/>
@@ -5951,8 +10300,8 @@
       <c r="E23" s="28"/>
       <c r="F23" s="28"/>
     </row>
-    <row r="24" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="39" t="s">
+    <row r="24" spans="1:6" ht="20" customHeight="1">
+      <c r="A24" s="45" t="s">
         <v>105</v>
       </c>
       <c r="B24" s="28"/>
@@ -5961,7 +10310,7 @@
       <c r="E24" s="28"/>
       <c r="F24" s="28"/>
     </row>
-    <row r="25" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="36" customHeight="1">
       <c r="A25" s="10" t="s">
         <v>106</v>
       </c>
@@ -5979,7 +10328,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="36" customHeight="1">
       <c r="A26" s="10" t="s">
         <v>106</v>
       </c>
@@ -5997,7 +10346,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="38" customHeight="1">
       <c r="A27" s="10" t="s">
         <v>106</v>
       </c>
@@ -6015,8 +10364,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="44" t="s">
+    <row r="28" spans="1:6" ht="25" customHeight="1">
+      <c r="A28" s="33" t="s">
         <v>119</v>
       </c>
       <c r="B28" s="28"/>
@@ -6025,8 +10374,8 @@
       <c r="E28" s="28"/>
       <c r="F28" s="28"/>
     </row>
-    <row r="29" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="37" t="s">
+    <row r="29" spans="1:6" ht="20" customHeight="1">
+      <c r="A29" s="43" t="s">
         <v>120</v>
       </c>
       <c r="B29" s="28"/>
@@ -6035,7 +10384,7 @@
       <c r="E29" s="28"/>
       <c r="F29" s="28"/>
     </row>
-    <row r="30" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="35" customHeight="1">
       <c r="A30" s="12" t="s">
         <v>121</v>
       </c>
@@ -6053,7 +10402,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="35" customHeight="1">
       <c r="A31" s="12" t="s">
         <v>121</v>
       </c>
@@ -6071,7 +10420,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="35" customHeight="1">
       <c r="A32" s="12" t="s">
         <v>121</v>
       </c>
@@ -6089,7 +10438,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="35" customHeight="1">
       <c r="A33" s="12" t="s">
         <v>121</v>
       </c>
@@ -6107,7 +10456,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="35" customHeight="1">
       <c r="A34" s="12" t="s">
         <v>121</v>
       </c>
@@ -6125,7 +10474,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="35" customHeight="1">
       <c r="A35" s="12" t="s">
         <v>121</v>
       </c>
@@ -6143,7 +10492,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="35" customHeight="1">
       <c r="A36" s="12" t="s">
         <v>121</v>
       </c>
@@ -6161,7 +10510,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="35" customHeight="1">
       <c r="A37" s="12" t="s">
         <v>121</v>
       </c>
@@ -6179,8 +10528,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="40" t="s">
+    <row r="38" spans="1:6" ht="25" customHeight="1">
+      <c r="A38" s="46" t="s">
         <v>148</v>
       </c>
       <c r="B38" s="28"/>
@@ -6189,8 +10538,8 @@
       <c r="E38" s="28"/>
       <c r="F38" s="28"/>
     </row>
-    <row r="39" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="36" t="s">
+    <row r="39" spans="1:6" ht="20" customHeight="1">
+      <c r="A39" s="42" t="s">
         <v>149</v>
       </c>
       <c r="B39" s="28"/>
@@ -6199,7 +10548,7 @@
       <c r="E39" s="28"/>
       <c r="F39" s="28"/>
     </row>
-    <row r="40" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="35" customHeight="1">
       <c r="A40" s="13" t="s">
         <v>150</v>
       </c>
@@ -6217,7 +10566,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="37.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="37" customHeight="1">
       <c r="A41" s="13" t="s">
         <v>150</v>
       </c>
@@ -6235,7 +10584,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="35" customHeight="1">
       <c r="A42" s="13" t="s">
         <v>150</v>
       </c>
@@ -6253,7 +10602,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="36" customHeight="1">
       <c r="A43" s="13" t="s">
         <v>150</v>
       </c>
@@ -6271,7 +10620,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="44" customHeight="1">
       <c r="A44" s="13" t="s">
         <v>150</v>
       </c>
@@ -6289,7 +10638,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="35" customHeight="1">
       <c r="A45" s="13" t="s">
         <v>150</v>
       </c>
@@ -6307,7 +10656,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="39" customHeight="1">
       <c r="A46" s="13" t="s">
         <v>150</v>
       </c>
@@ -6325,8 +10674,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="43" t="s">
+    <row r="47" spans="1:6" ht="25" customHeight="1">
+      <c r="A47" s="32" t="s">
         <v>172</v>
       </c>
       <c r="B47" s="28"/>
@@ -6335,8 +10684,8 @@
       <c r="E47" s="28"/>
       <c r="F47" s="28"/>
     </row>
-    <row r="48" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="34" t="s">
+    <row r="48" spans="1:6" ht="20" customHeight="1">
+      <c r="A48" s="40" t="s">
         <v>173</v>
       </c>
       <c r="B48" s="28"/>
@@ -6345,7 +10694,7 @@
       <c r="E48" s="28"/>
       <c r="F48" s="28"/>
     </row>
-    <row r="49" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="35" customHeight="1">
       <c r="A49" s="14" t="s">
         <v>174</v>
       </c>
@@ -6363,7 +10712,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="35" customHeight="1">
       <c r="A50" s="14" t="s">
         <v>174</v>
       </c>
@@ -6381,7 +10730,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="35" customHeight="1">
       <c r="A51" s="14" t="s">
         <v>174</v>
       </c>
@@ -6399,7 +10748,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="36" customHeight="1">
       <c r="A52" s="14" t="s">
         <v>174</v>
       </c>
@@ -6417,8 +10766,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="38" t="s">
+    <row r="53" spans="1:6" ht="25" customHeight="1">
+      <c r="A53" s="44" t="s">
         <v>187</v>
       </c>
       <c r="B53" s="28"/>
@@ -6427,8 +10776,8 @@
       <c r="E53" s="28"/>
       <c r="F53" s="28"/>
     </row>
-    <row r="54" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="41" t="s">
+    <row r="54" spans="1:6" ht="20" customHeight="1">
+      <c r="A54" s="47" t="s">
         <v>188</v>
       </c>
       <c r="B54" s="28"/>
@@ -6437,7 +10786,7 @@
       <c r="E54" s="28"/>
       <c r="F54" s="28"/>
     </row>
-    <row r="55" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="35" customHeight="1">
       <c r="A55" s="15" t="s">
         <v>189</v>
       </c>
@@ -6455,7 +10804,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="35" customHeight="1">
       <c r="A56" s="15" t="s">
         <v>189</v>
       </c>
@@ -6473,7 +10822,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="36" customHeight="1">
       <c r="A57" s="15" t="s">
         <v>189</v>
       </c>
@@ -6491,7 +10840,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="35" customHeight="1">
       <c r="A58" s="15" t="s">
         <v>189</v>
       </c>
@@ -6509,7 +10858,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="37.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="37" customHeight="1">
       <c r="A59" s="15" t="s">
         <v>189</v>
       </c>
@@ -6527,7 +10876,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="35" customHeight="1">
       <c r="A60" s="15" t="s">
         <v>189</v>
       </c>
@@ -6545,7 +10894,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="35" customHeight="1">
       <c r="A61" s="15" t="s">
         <v>189</v>
       </c>
@@ -6563,7 +10912,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="36" customHeight="1">
       <c r="A62" s="15" t="s">
         <v>189</v>
       </c>
@@ -6581,8 +10930,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="42" t="s">
+    <row r="63" spans="1:6" ht="25" customHeight="1">
+      <c r="A63" s="48" t="s">
         <v>217</v>
       </c>
       <c r="B63" s="28"/>
@@ -6591,8 +10940,8 @@
       <c r="E63" s="28"/>
       <c r="F63" s="28"/>
     </row>
-    <row r="64" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="30" t="s">
+    <row r="64" spans="1:6" ht="20" customHeight="1">
+      <c r="A64" s="36" t="s">
         <v>218</v>
       </c>
       <c r="B64" s="28"/>
@@ -6601,7 +10950,7 @@
       <c r="E64" s="28"/>
       <c r="F64" s="28"/>
     </row>
-    <row r="65" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" ht="35" customHeight="1">
       <c r="A65" s="16" t="s">
         <v>219</v>
       </c>
@@ -6619,7 +10968,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" ht="35" customHeight="1">
       <c r="A66" s="16" t="s">
         <v>219</v>
       </c>
@@ -6639,6 +10988,8 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A23:F23"/>
@@ -6654,17 +11005,15 @@
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A63:F63"/>
-    <mergeCell ref="A47:F47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -6673,7 +11022,7 @@
     <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="30" customHeight="1">
       <c r="A1" s="50" t="s">
         <v>253</v>
       </c>
@@ -6682,7 +11031,7 @@
       <c r="D1" s="28"/>
       <c r="E1" s="28"/>
     </row>
-    <row r="2" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="25" customHeight="1">
       <c r="A2" s="17" t="s">
         <v>28</v>
       </c>
@@ -6699,7 +11048,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="20" customHeight="1">
       <c r="A3" s="18" t="s">
         <v>36</v>
       </c>
@@ -6716,7 +11065,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="20" customHeight="1">
       <c r="A4" s="18" t="s">
         <v>36</v>
       </c>
@@ -6733,7 +11082,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="20" customHeight="1">
       <c r="A5" s="18" t="s">
         <v>36</v>
       </c>
@@ -6750,7 +11099,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="20" customHeight="1">
       <c r="A6" s="18" t="s">
         <v>36</v>
       </c>
@@ -6767,7 +11116,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="20" customHeight="1">
       <c r="A7" s="18" t="s">
         <v>36</v>
       </c>
@@ -6784,7 +11133,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="20" customHeight="1">
       <c r="A8" s="18" t="s">
         <v>36</v>
       </c>
@@ -6801,7 +11150,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="20" customHeight="1">
       <c r="A9" s="18" t="s">
         <v>36</v>
       </c>
@@ -6818,7 +11167,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="20" customHeight="1">
       <c r="A10" s="18" t="s">
         <v>36</v>
       </c>
@@ -6835,7 +11184,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="20" customHeight="1">
       <c r="A11" s="18" t="s">
         <v>36</v>
       </c>
@@ -6852,7 +11201,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="20" customHeight="1">
       <c r="A12" s="18" t="s">
         <v>36</v>
       </c>
@@ -6869,7 +11218,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="20" customHeight="1">
       <c r="A13" s="18" t="s">
         <v>36</v>
       </c>
@@ -6886,7 +11235,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="20" customHeight="1">
       <c r="A14" s="18" t="s">
         <v>36</v>
       </c>
@@ -6903,7 +11252,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="20" customHeight="1">
       <c r="A15" s="18" t="s">
         <v>88</v>
       </c>
@@ -6920,7 +11269,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="20" customHeight="1">
       <c r="A16" s="18" t="s">
         <v>88</v>
       </c>
@@ -6937,7 +11286,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="20" customHeight="1">
       <c r="A17" s="18" t="s">
         <v>88</v>
       </c>
@@ -6954,7 +11303,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="20" customHeight="1">
       <c r="A18" s="18" t="s">
         <v>88</v>
       </c>
@@ -6971,7 +11320,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="20" customHeight="1">
       <c r="A19" s="18" t="s">
         <v>106</v>
       </c>
@@ -6988,7 +11337,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="20" customHeight="1">
       <c r="A20" s="18" t="s">
         <v>106</v>
       </c>
@@ -7005,7 +11354,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="20" customHeight="1">
       <c r="A21" s="18" t="s">
         <v>106</v>
       </c>
@@ -7022,7 +11371,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="20" customHeight="1">
       <c r="A22" s="18" t="s">
         <v>121</v>
       </c>
@@ -7039,7 +11388,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="20" customHeight="1">
       <c r="A23" s="18" t="s">
         <v>121</v>
       </c>
@@ -7056,7 +11405,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="20" customHeight="1">
       <c r="A24" s="18" t="s">
         <v>121</v>
       </c>
@@ -7073,7 +11422,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="20" customHeight="1">
       <c r="A25" s="18" t="s">
         <v>121</v>
       </c>
@@ -7090,7 +11439,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="20" customHeight="1">
       <c r="A26" s="18" t="s">
         <v>121</v>
       </c>
@@ -7107,7 +11456,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="20" customHeight="1">
       <c r="A27" s="18" t="s">
         <v>121</v>
       </c>
@@ -7124,7 +11473,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="20" customHeight="1">
       <c r="A28" s="18" t="s">
         <v>121</v>
       </c>
@@ -7141,7 +11490,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="20" customHeight="1">
       <c r="A29" s="18" t="s">
         <v>121</v>
       </c>
@@ -7158,7 +11507,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="20" customHeight="1">
       <c r="A30" s="18" t="s">
         <v>150</v>
       </c>
@@ -7175,7 +11524,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="20" customHeight="1">
       <c r="A31" s="18" t="s">
         <v>150</v>
       </c>
@@ -7192,7 +11541,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="20" customHeight="1">
       <c r="A32" s="18" t="s">
         <v>150</v>
       </c>
@@ -7209,7 +11558,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="20" customHeight="1">
       <c r="A33" s="18" t="s">
         <v>150</v>
       </c>
@@ -7226,7 +11575,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="20" customHeight="1">
       <c r="A34" s="18" t="s">
         <v>150</v>
       </c>
@@ -7243,7 +11592,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="20" customHeight="1">
       <c r="A35" s="18" t="s">
         <v>150</v>
       </c>
@@ -7260,7 +11609,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" ht="20" customHeight="1">
       <c r="A36" s="18" t="s">
         <v>150</v>
       </c>
@@ -7277,7 +11626,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="20" customHeight="1">
       <c r="A37" s="18" t="s">
         <v>174</v>
       </c>
@@ -7294,7 +11643,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="20" customHeight="1">
       <c r="A38" s="18" t="s">
         <v>174</v>
       </c>
@@ -7311,7 +11660,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="20" customHeight="1">
       <c r="A39" s="18" t="s">
         <v>174</v>
       </c>
@@ -7328,7 +11677,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="20" customHeight="1">
       <c r="A40" s="18" t="s">
         <v>174</v>
       </c>
@@ -7345,7 +11694,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" ht="20" customHeight="1">
       <c r="A41" s="18" t="s">
         <v>189</v>
       </c>
@@ -7362,7 +11711,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" ht="20" customHeight="1">
       <c r="A42" s="18" t="s">
         <v>189</v>
       </c>
@@ -7379,7 +11728,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" ht="20" customHeight="1">
       <c r="A43" s="18" t="s">
         <v>189</v>
       </c>
@@ -7396,7 +11745,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" ht="20" customHeight="1">
       <c r="A44" s="18" t="s">
         <v>189</v>
       </c>
@@ -7413,7 +11762,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" ht="20" customHeight="1">
       <c r="A45" s="18" t="s">
         <v>189</v>
       </c>
@@ -7430,7 +11779,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" ht="20" customHeight="1">
       <c r="A46" s="18" t="s">
         <v>189</v>
       </c>
@@ -7447,7 +11796,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" ht="20" customHeight="1">
       <c r="A47" s="18" t="s">
         <v>189</v>
       </c>
@@ -7464,7 +11813,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" ht="20" customHeight="1">
       <c r="A48" s="18" t="s">
         <v>189</v>
       </c>
@@ -7481,7 +11830,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" ht="20" customHeight="1">
       <c r="A49" s="18" t="s">
         <v>219</v>
       </c>
@@ -7498,7 +11847,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" ht="20" customHeight="1">
       <c r="A50" s="18" t="s">
         <v>219</v>
       </c>
@@ -7523,29 +11872,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="30" customHeight="1">
       <c r="A1" s="50" t="s">
         <v>267</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
     </row>
-    <row r="3" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="20" customHeight="1">
       <c r="A3" s="19"/>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
     </row>
-    <row r="4" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="20" customHeight="1">
       <c r="A4" s="20" t="s">
         <v>268</v>
       </c>
@@ -7556,7 +11905,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="20" customHeight="1">
       <c r="A5" s="19" t="s">
         <v>271</v>
       </c>
@@ -7567,7 +11916,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="20" customHeight="1">
       <c r="A6" s="19" t="s">
         <v>274</v>
       </c>
@@ -7578,7 +11927,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="20" customHeight="1">
       <c r="A7" s="19" t="s">
         <v>275</v>
       </c>
@@ -7589,7 +11938,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="20" customHeight="1">
       <c r="A8" s="19" t="s">
         <v>276</v>
       </c>
@@ -7600,12 +11949,12 @@
         <v>277</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="20" customHeight="1">
       <c r="A9" s="19"/>
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
     </row>
-    <row r="10" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="20" customHeight="1">
       <c r="A10" s="20" t="s">
         <v>278</v>
       </c>
@@ -7616,7 +11965,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="20" customHeight="1">
       <c r="A11" s="19" t="s">
         <v>281</v>
       </c>
@@ -7627,7 +11976,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="20" customHeight="1">
       <c r="A12" s="19" t="s">
         <v>284</v>
       </c>
@@ -7638,7 +11987,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="20" customHeight="1">
       <c r="A13" s="19" t="s">
         <v>287</v>
       </c>
@@ -7649,7 +11998,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="20" customHeight="1">
       <c r="A14" s="19" t="s">
         <v>289</v>
       </c>
@@ -7660,7 +12009,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="20" customHeight="1">
       <c r="A15" s="19" t="s">
         <v>291</v>
       </c>
@@ -7671,7 +12020,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="20" customHeight="1">
       <c r="A16" s="19" t="s">
         <v>293</v>
       </c>
@@ -7682,7 +12031,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="20" customHeight="1">
       <c r="A17" s="19" t="s">
         <v>295</v>
       </c>
@@ -7693,7 +12042,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="20" customHeight="1">
       <c r="A18" s="19" t="s">
         <v>298</v>
       </c>
@@ -7704,7 +12053,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="20" customHeight="1">
       <c r="A19" s="19" t="s">
         <v>300</v>
       </c>
@@ -7715,7 +12064,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="20" customHeight="1">
       <c r="A20" s="19" t="s">
         <v>302</v>
       </c>
@@ -7726,7 +12075,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="20" customHeight="1">
       <c r="A21" s="19" t="s">
         <v>304</v>
       </c>
@@ -7737,7 +12086,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="20" customHeight="1">
       <c r="A22" s="19" t="s">
         <v>306</v>
       </c>
@@ -7748,7 +12097,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="20" customHeight="1">
       <c r="A23" s="19" t="s">
         <v>308</v>
       </c>
@@ -7759,7 +12108,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="20" customHeight="1">
       <c r="A24" s="19" t="s">
         <v>310</v>
       </c>
@@ -7770,7 +12119,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="20" customHeight="1">
       <c r="A25" s="19" t="s">
         <v>313</v>
       </c>
@@ -7781,7 +12130,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="20" customHeight="1">
       <c r="A26" s="19" t="s">
         <v>315</v>
       </c>
@@ -7792,7 +12141,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="20" customHeight="1">
       <c r="A27" s="19" t="s">
         <v>317</v>
       </c>
@@ -7803,7 +12152,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="20" customHeight="1">
       <c r="A28" s="19" t="s">
         <v>319</v>
       </c>
@@ -7814,19 +12163,19 @@
         <v>321</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="20" customHeight="1">
       <c r="A29" s="19"/>
       <c r="B29" s="19"/>
       <c r="C29" s="19"/>
     </row>
-    <row r="30" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="20" customHeight="1">
       <c r="A30" s="20" t="s">
         <v>322</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
     </row>
-    <row r="31" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="20" customHeight="1">
       <c r="A31" s="19" t="s">
         <v>323</v>
       </c>
@@ -7837,7 +12186,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="20" customHeight="1">
       <c r="A32" s="19" t="s">
         <v>326</v>
       </c>
@@ -7848,7 +12197,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="20" customHeight="1">
       <c r="A33" s="19" t="s">
         <v>329</v>
       </c>
@@ -7857,7 +12206,7 @@
       </c>
       <c r="C33" s="19"/>
     </row>
-    <row r="34" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="20" customHeight="1">
       <c r="A34" s="19" t="s">
         <v>331</v>
       </c>
